--- a/Sensitivity/Harmonization_SAF/Harmonization Sheets/Schmidt_Concawe_2024_Harmonization.xlsx
+++ b/Sensitivity/Harmonization_SAF/Harmonization Sheets/Schmidt_Concawe_2024_Harmonization.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="104" documentId="13_ncr:1_{409032AC-1BE5-8741-8011-1AD30BF05070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38530D46-E5A1-4666-9CB4-4BF82CAEBC5C}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs" sheetId="1" r:id="rId1"/>
@@ -849,6 +849,9 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -856,19 +859,16 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -987,7 +987,7 @@
         </row>
         <row r="19">
           <cell r="C19">
-            <v>0.8</v>
+            <v>1.7</v>
           </cell>
         </row>
         <row r="21">
@@ -1032,12 +1032,12 @@
         </row>
         <row r="33">
           <cell r="C33">
-            <v>1282</v>
+            <v>1371</v>
           </cell>
         </row>
         <row r="34">
           <cell r="C34">
-            <v>480</v>
+            <v>523</v>
           </cell>
         </row>
       </sheetData>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="C18" s="5">
         <f>[1]Inputs!C19</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="D18" t="s">
         <v>21</v>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="C32" s="5">
         <f>[1]Inputs!C33</f>
-        <v>1282</v>
+        <v>1371</v>
       </c>
       <c r="D32" t="s">
         <v>29</v>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="C33" s="9">
         <f>[1]Inputs!$C$34</f>
-        <v>480</v>
+        <v>523</v>
       </c>
       <c r="D33" t="s">
         <v>29</v>
@@ -1811,7 +1811,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="51" t="s">
         <v>160</v>
       </c>
       <c r="B1" s="42"/>
@@ -1819,7 +1819,7 @@
       <c r="D1" s="42"/>
       <c r="E1" s="42"/>
       <c r="F1" s="42"/>
-      <c r="H1" s="49" t="s">
+      <c r="H1" s="51" t="s">
         <v>161</v>
       </c>
       <c r="I1" s="42"/>
@@ -1827,7 +1827,7 @@
       <c r="K1" s="42"/>
       <c r="L1" s="42"/>
       <c r="M1" s="42"/>
-      <c r="O1" s="49" t="s">
+      <c r="O1" s="51" t="s">
         <v>162</v>
       </c>
       <c r="P1" s="42"/>
@@ -1909,11 +1909,11 @@
       </c>
       <c r="E3" s="32">
         <f>'MFSP CO2 Corrected'!B9</f>
-        <v>7.0437610212511137</v>
+        <v>7.2917372712511144</v>
       </c>
       <c r="F3" s="32">
         <f>'MFSP WACC Corrected'!B9</f>
-        <v>6.7170632102834826</v>
+        <v>6.965039460283486</v>
       </c>
       <c r="H3" s="22" t="s">
         <v>167</v>
@@ -1931,11 +1931,11 @@
       </c>
       <c r="L3" s="32">
         <f>'MFSP CO2 Corrected'!B31</f>
-        <v>6.6539799540486122</v>
+        <v>6.9019562040486138</v>
       </c>
       <c r="M3" s="32">
         <f>'MFSP WACC Corrected'!B31</f>
-        <v>6.3945065003377843</v>
+        <v>6.6424827503377841</v>
       </c>
       <c r="N3" s="5"/>
       <c r="O3" s="34" t="s">
@@ -1954,11 +1954,11 @@
       </c>
       <c r="S3" s="32">
         <f>'MFSP CO2 Corrected'!B55</f>
-        <v>7.0996864457224591</v>
+        <v>7.3476626957224616</v>
       </c>
       <c r="T3" s="32">
         <f>'MFSP WACC Corrected'!B55</f>
-        <v>6.7644023461332434</v>
+        <v>7.0123785961332468</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -1978,11 +1978,11 @@
       </c>
       <c r="E4" s="32">
         <f>E3/Inputs!$C$6</f>
-        <v>7.8264011347234597</v>
+        <v>8.1019303013901265</v>
       </c>
       <c r="F4" s="32">
         <f>F3/Inputs!$C$6</f>
-        <v>7.463403566981647</v>
+        <v>7.7389327336483174</v>
       </c>
       <c r="H4" s="22" t="s">
         <v>167</v>
@@ -2000,11 +2000,11 @@
       </c>
       <c r="L4" s="32">
         <f>L3/Inputs!$C$6</f>
-        <v>7.3933110600540131</v>
+        <v>7.6688402267206817</v>
       </c>
       <c r="M4" s="32">
         <f>M3/Inputs!$C$6</f>
-        <v>7.1050072225975383</v>
+        <v>7.3805363892642042</v>
       </c>
       <c r="N4" s="5"/>
       <c r="O4" s="34" t="s">
@@ -2023,11 +2023,11 @@
       </c>
       <c r="S4" s="32">
         <f>S3/Inputs!$C$6</f>
-        <v>7.8885404952471765</v>
+        <v>8.164069661913846</v>
       </c>
       <c r="T4" s="32">
         <f>T3/Inputs!$C$6</f>
-        <v>7.5160026068147143</v>
+        <v>7.7915317734813847</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -2387,11 +2387,11 @@
       </c>
       <c r="E10" s="33">
         <f>((E4-E5)/E9) * 10^6</f>
-        <v>2446.2639259614443</v>
+        <v>2542.1902825760685</v>
       </c>
       <c r="F10" s="33">
         <f>((F4-F5)/F9) * 10^6</f>
-        <v>2319.8851670274812</v>
+        <v>2415.8115236421067</v>
       </c>
       <c r="H10" s="22" t="s">
         <v>175</v>
@@ -2409,11 +2409,11 @@
       </c>
       <c r="L10" s="33">
         <f>((L4-L5)/L9) * 10^6</f>
-        <v>2295.4822375775925</v>
+        <v>2391.4085941922176</v>
       </c>
       <c r="M10" s="33">
         <f>((M4-M5)/M9) * 10^6</f>
-        <v>2195.1083386550417</v>
+        <v>2291.0346952696664</v>
       </c>
       <c r="O10" s="22" t="s">
         <v>175</v>
@@ -2431,15 +2431,15 @@
       </c>
       <c r="S10" s="33">
         <f>((S4-S5)/S9) * 10^6</f>
-        <v>2467.8979421692966</v>
+        <v>2563.8242987839221</v>
       </c>
       <c r="T10" s="33">
         <f>((T4-T5)/T9) * 10^6</f>
-        <v>2338.1976902120696</v>
+        <v>2434.1240468266951</v>
       </c>
     </row>
     <row r="12" spans="1:20">
-      <c r="A12" s="49" t="s">
+      <c r="A12" s="51" t="s">
         <v>176</v>
       </c>
       <c r="B12" s="42"/>
@@ -2447,7 +2447,7 @@
       <c r="D12" s="42"/>
       <c r="E12" s="42"/>
       <c r="F12" s="42"/>
-      <c r="H12" s="49" t="s">
+      <c r="H12" s="51" t="s">
         <v>177</v>
       </c>
       <c r="I12" s="42"/>
@@ -2455,7 +2455,7 @@
       <c r="K12" s="42"/>
       <c r="L12" s="42"/>
       <c r="M12" s="42"/>
-      <c r="O12" s="49" t="s">
+      <c r="O12" s="51" t="s">
         <v>178</v>
       </c>
       <c r="P12" s="42"/>
@@ -2537,11 +2537,11 @@
       </c>
       <c r="E14" s="32">
         <f>'MFSP CO2 Corrected'!B19</f>
-        <v>2.7886431036926567</v>
+        <v>2.9084518536926556</v>
       </c>
       <c r="F14" s="32">
         <f>'MFSP WACC Corrected'!B19</f>
-        <v>2.5930432604594715</v>
+        <v>2.7128520104594722</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="34" t="s">
@@ -2560,11 +2560,11 @@
       </c>
       <c r="L14" s="32">
         <f>'MFSP CO2 Corrected'!B42</f>
-        <v>2.8027407526684223</v>
+        <v>2.9225495026684225</v>
       </c>
       <c r="M14" s="32">
         <f>'MFSP WACC Corrected'!B42</f>
-        <v>2.6053608252088116</v>
+        <v>2.7251695752088123</v>
       </c>
       <c r="N14" s="5"/>
       <c r="O14" s="34" t="s">
@@ -2583,11 +2583,11 @@
       </c>
       <c r="S14" s="32">
         <f>'MFSP CO2 Corrected'!B65</f>
-        <v>2.7872301230814234</v>
+        <v>2.9070388730814232</v>
       </c>
       <c r="T14" s="16">
         <f>'MFSP WACC Corrected'!B65</f>
-        <v>2.5921014786140577</v>
+        <v>2.7119102286140579</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -2607,11 +2607,11 @@
       </c>
       <c r="E15" s="32">
         <f>E14/Inputs!$C$6</f>
-        <v>3.0984923374362849</v>
+        <v>3.2316131707696174</v>
       </c>
       <c r="F15" s="32">
         <f>F14/Inputs!$C$6</f>
-        <v>2.8811591782883017</v>
+        <v>3.0142800116216355</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="34" t="s">
@@ -2630,11 +2630,11 @@
       </c>
       <c r="L15" s="32">
         <f>L14/Inputs!$C$6</f>
-        <v>3.1141563918538022</v>
+        <v>3.247277225187136</v>
       </c>
       <c r="M15" s="32">
         <f>M14/Inputs!$C$6</f>
-        <v>2.894845361343124</v>
+        <v>3.0279661946764582</v>
       </c>
       <c r="N15" s="5"/>
       <c r="O15" s="34" t="s">
@@ -2653,11 +2653,11 @@
       </c>
       <c r="S15" s="32">
         <f>S14/Inputs!$C$6</f>
-        <v>3.0969223589793593</v>
+        <v>3.2300431923126922</v>
       </c>
       <c r="T15" s="32">
         <f>T14/Inputs!$C$6</f>
-        <v>2.8801127540156197</v>
+        <v>3.0132335873489531</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -2669,19 +2669,19 @@
       </c>
       <c r="C16" s="32">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="D16" s="32">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="E16" s="32">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="F16" s="32">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="H16" s="22" t="s">
         <v>169</v>
@@ -2691,19 +2691,19 @@
       </c>
       <c r="J16" s="32">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="K16" s="32">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="L16" s="32">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="M16" s="32">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="O16" s="22" t="s">
         <v>169</v>
@@ -2713,19 +2713,19 @@
       </c>
       <c r="Q16" s="32">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="R16" s="32">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="S16" s="32">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="T16" s="32">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="17" spans="1:20">
@@ -3009,19 +3009,19 @@
       </c>
       <c r="C21" s="33">
         <f>((C15-C16)/C20) * 10^6</f>
-        <v>832.71052901141434</v>
+        <v>519.37266355919519</v>
       </c>
       <c r="D21" s="33">
         <f>((D15-D16)/D20) * 10^6</f>
-        <v>453.16802271738186</v>
+        <v>139.83015726516268</v>
       </c>
       <c r="E21" s="33">
         <f>((E15-E16)/E20) * 10^6</f>
-        <v>800.22742530063044</v>
+        <v>533.23600180828578</v>
       </c>
       <c r="F21" s="33">
         <f>((F15-F16)/F20) * 10^6</f>
-        <v>724.56219399016777</v>
+        <v>457.5707704978235</v>
       </c>
       <c r="H21" s="22" t="s">
         <v>175</v>
@@ -3031,19 +3031,19 @@
       </c>
       <c r="J21" s="33">
         <f>((J15-J16)/J20) * 10^6</f>
-        <v>986.77532731178451</v>
+        <v>673.43746185956547</v>
       </c>
       <c r="K21" s="33">
         <f>((K15-K16)/K20) * 10^6</f>
-        <v>458.62151313461851</v>
+        <v>145.28364768239931</v>
       </c>
       <c r="L21" s="33">
         <f>((L15-L16)/L20) * 10^6</f>
-        <v>805.68091571786647</v>
+        <v>538.68949222552214</v>
       </c>
       <c r="M21" s="33">
         <f>((M15-M16)/M20) * 10^6</f>
-        <v>729.32708219526364</v>
+        <v>462.33565870291955</v>
       </c>
       <c r="O21" s="22" t="s">
         <v>175</v>
@@ -3053,37 +3053,37 @@
       </c>
       <c r="Q21" s="33">
         <f>((Q15-Q16)/Q20) * 10^6</f>
-        <v>832.16393601308198</v>
+        <v>518.82607056086272</v>
       </c>
       <c r="R21" s="33">
         <f>((R15-R16)/R20) * 10^6</f>
-        <v>452.62142971905007</v>
+        <v>139.28356426683089</v>
       </c>
       <c r="S21" s="33">
         <f>((S15-S16)/S20) * 10^6</f>
-        <v>799.68083230229831</v>
+        <v>532.68940880995365</v>
       </c>
       <c r="T21" s="33">
         <f>((T15-T16)/T20) * 10^6</f>
-        <v>724.19787804799034</v>
+        <v>457.20645455564602</v>
       </c>
     </row>
     <row r="23" spans="1:20">
-      <c r="A23" s="51" t="s">
+      <c r="A23" s="50" t="s">
         <v>179</v>
       </c>
-      <c r="B23" s="51"/>
-      <c r="C23" s="51"/>
-      <c r="H23" s="51" t="s">
+      <c r="B23" s="50"/>
+      <c r="C23" s="50"/>
+      <c r="H23" s="50" t="s">
         <v>180</v>
       </c>
-      <c r="I23" s="51"/>
-      <c r="J23" s="51"/>
-      <c r="O23" s="51" t="s">
+      <c r="I23" s="50"/>
+      <c r="J23" s="50"/>
+      <c r="O23" s="50" t="s">
         <v>181</v>
       </c>
-      <c r="P23" s="51"/>
-      <c r="Q23" s="51"/>
+      <c r="P23" s="50"/>
+      <c r="Q23" s="50"/>
     </row>
     <row r="24" spans="1:20">
       <c r="A24" s="37" t="s">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="C26" s="9">
         <f>C25*Inputs!$C$32 * 10^-6</f>
-        <v>0.26238519648000003</v>
+        <v>0.28060070544000004</v>
       </c>
       <c r="H26" s="37" t="s">
         <v>183</v>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="J26" s="9">
         <f>J25*Inputs!$C$32 * 10^-6</f>
-        <v>0.26238519648000003</v>
+        <v>0.28060070544000004</v>
       </c>
       <c r="O26" s="37" t="s">
         <v>183</v>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="Q26" s="9">
         <f>Q25*Inputs!$C$32 * 10^-6</f>
-        <v>0.26238519648000003</v>
+        <v>0.28060070544000004</v>
       </c>
     </row>
     <row r="27" spans="1:20">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="C27" s="9">
         <f>F4+C26</f>
-        <v>7.7257887634616473</v>
+        <v>8.0195334390883168</v>
       </c>
       <c r="H27" s="37" t="s">
         <v>184</v>
@@ -3197,7 +3197,7 @@
       </c>
       <c r="J27" s="9">
         <f>M4+J26</f>
-        <v>7.3673924190775386</v>
+        <v>7.6611370947042046</v>
       </c>
       <c r="O27" s="37" t="s">
         <v>184</v>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="Q27" s="9">
         <f>T4+Q26</f>
-        <v>7.7783878032947147</v>
+        <v>8.0721324789213842</v>
       </c>
     </row>
     <row r="28" spans="1:20">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="C28" s="5">
         <f>(C27-C16) /C20 * 10^6</f>
-        <v>2411.2354085733746</v>
+        <v>2200.1656871753949</v>
       </c>
       <c r="H28" s="37" t="s">
         <v>185</v>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="J28" s="5">
         <f>(J27-J16) /J20 * 10^6</f>
-        <v>2286.458580200936</v>
+        <v>2075.388858802954</v>
       </c>
       <c r="O28" s="37" t="s">
         <v>185</v>
@@ -3239,25 +3239,25 @@
       </c>
       <c r="Q28" s="5">
         <f>(Q27-Q16) /Q20 * 10^6</f>
-        <v>2429.5479317579629</v>
+        <v>2218.4782103599828</v>
       </c>
     </row>
     <row r="30" spans="1:20">
-      <c r="A30" s="51" t="s">
+      <c r="A30" s="50" t="s">
         <v>186</v>
       </c>
-      <c r="B30" s="51"/>
-      <c r="C30" s="51"/>
-      <c r="H30" s="51" t="s">
+      <c r="B30" s="50"/>
+      <c r="C30" s="50"/>
+      <c r="H30" s="50" t="s">
         <v>187</v>
       </c>
-      <c r="I30" s="51"/>
-      <c r="J30" s="51"/>
-      <c r="O30" s="51" t="s">
+      <c r="I30" s="50"/>
+      <c r="J30" s="50"/>
+      <c r="O30" s="50" t="s">
         <v>188</v>
       </c>
-      <c r="P30" s="51"/>
-      <c r="Q30" s="51"/>
+      <c r="P30" s="50"/>
+      <c r="Q30" s="50"/>
     </row>
     <row r="31" spans="1:20">
       <c r="A31" s="37" t="s">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="C33" s="9">
         <f>C32*Inputs!$C$33 * 10^-6</f>
-        <v>5.3146579433265506E-2</v>
+        <v>5.7907627174162202E-2</v>
       </c>
       <c r="H33" s="37" t="s">
         <v>183</v>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="J33" s="9">
         <f>J32*Inputs!$C$33 * 10^-6</f>
-        <v>6.051498595120719E-2</v>
+        <v>6.5936120109336166E-2</v>
       </c>
       <c r="O33" s="37" t="s">
         <v>183</v>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="Q33" s="9">
         <f>Q32*Inputs!$C$33 * 10^-6</f>
-        <v>5.3120437709419398E-2</v>
+        <v>5.7879143587554881E-2</v>
       </c>
     </row>
     <row r="34" spans="1:17">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="C34" s="9">
         <f>F15+C33</f>
-        <v>2.9343057577215674</v>
+        <v>3.0721876387957976</v>
       </c>
       <c r="H34" s="37" t="s">
         <v>184</v>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="J34" s="9">
         <f>M15+J33</f>
-        <v>2.9553603472943313</v>
+        <v>3.0939023147857942</v>
       </c>
       <c r="O34" s="37" t="s">
         <v>184</v>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="Q34" s="9">
         <f>T15+Q33</f>
-        <v>2.9332331917250389</v>
+        <v>3.0711127309365081</v>
       </c>
     </row>
     <row r="35" spans="1:17">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="C35" s="5">
         <f>(C34-C16) /C20 * 10^6</f>
-        <v>743.06534482984148</v>
+        <v>477.73149526688445</v>
       </c>
       <c r="H35" s="37" t="s">
         <v>185</v>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="J35" s="5">
         <f>(J34-J16) /J20 * 10^6</f>
-        <v>750.39556722395503</v>
+        <v>485.29152884876459</v>
       </c>
       <c r="O35" s="37" t="s">
         <v>185</v>
@@ -3413,15 +3413,15 @@
       </c>
       <c r="Q35" s="5">
         <f>(Q34-Q16) /Q20 * 10^6</f>
-        <v>742.69192756327607</v>
+        <v>477.35726267334269</v>
       </c>
     </row>
     <row r="38" spans="1:17">
-      <c r="A38" s="50" t="s">
+      <c r="A38" s="49" t="s">
         <v>189</v>
       </c>
-      <c r="B38" s="50"/>
-      <c r="C38" s="50"/>
+      <c r="B38" s="49"/>
+      <c r="C38" s="49"/>
     </row>
     <row r="39" spans="1:17">
       <c r="A39" s="21" t="s">
@@ -3532,6 +3532,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="O1:T1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="O12:T12"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="H12:M12"/>
     <mergeCell ref="A38:C38"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="H23:J23"/>
@@ -3539,12 +3545,6 @@
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="H30:J30"/>
     <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="H1:M1"/>
-    <mergeCell ref="O1:T1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="O12:T12"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="H12:M12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5814,14 +5814,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="47" t="s">
         <v>117</v>
       </c>
       <c r="B1" s="39"/>
       <c r="C1" s="39"/>
       <c r="D1" s="39"/>
       <c r="E1" s="40"/>
-      <c r="G1" s="46" t="s">
+      <c r="G1" s="47" t="s">
         <v>118</v>
       </c>
       <c r="H1" s="39"/>
@@ -5829,7 +5829,7 @@
       <c r="J1" s="39"/>
       <c r="K1" s="40"/>
       <c r="L1" s="23"/>
-      <c r="M1" s="46" t="s">
+      <c r="M1" s="47" t="s">
         <v>119</v>
       </c>
       <c r="N1" s="39"/>
@@ -5839,21 +5839,21 @@
       <c r="R1" s="23"/>
     </row>
     <row r="2" spans="1:18">
-      <c r="A2" s="47" t="s">
+      <c r="A2" s="44" t="s">
         <v>87</v>
       </c>
       <c r="B2" s="39"/>
       <c r="C2" s="39"/>
       <c r="D2" s="39"/>
       <c r="E2" s="40"/>
-      <c r="G2" s="47" t="s">
+      <c r="G2" s="44" t="s">
         <v>87</v>
       </c>
       <c r="H2" s="39"/>
       <c r="I2" s="39"/>
       <c r="J2" s="39"/>
       <c r="K2" s="40"/>
-      <c r="M2" s="47" t="s">
+      <c r="M2" s="44" t="s">
         <v>87</v>
       </c>
       <c r="N2" s="39"/>
@@ -6161,21 +6161,21 @@
       <c r="Q9" s="30"/>
     </row>
     <row r="10" spans="1:18">
-      <c r="A10" s="47" t="s">
+      <c r="A10" s="44" t="s">
         <v>95</v>
       </c>
       <c r="B10" s="39"/>
       <c r="C10" s="39"/>
       <c r="D10" s="39"/>
       <c r="E10" s="40"/>
-      <c r="G10" s="47" t="s">
+      <c r="G10" s="44" t="s">
         <v>95</v>
       </c>
       <c r="H10" s="39"/>
       <c r="I10" s="39"/>
       <c r="J10" s="39"/>
       <c r="K10" s="40"/>
-      <c r="M10" s="47" t="s">
+      <c r="M10" s="44" t="s">
         <v>95</v>
       </c>
       <c r="N10" s="39"/>
@@ -6521,21 +6521,21 @@
       <c r="Q18" s="30"/>
     </row>
     <row r="21" spans="1:17">
-      <c r="A21" s="46" t="s">
+      <c r="A21" s="47" t="s">
         <v>131</v>
       </c>
       <c r="B21" s="39"/>
       <c r="C21" s="39"/>
       <c r="D21" s="39"/>
       <c r="E21" s="40"/>
-      <c r="G21" s="46" t="s">
+      <c r="G21" s="47" t="s">
         <v>132</v>
       </c>
       <c r="H21" s="39"/>
       <c r="I21" s="39"/>
       <c r="J21" s="39"/>
       <c r="K21" s="40"/>
-      <c r="M21" s="46" t="s">
+      <c r="M21" s="47" t="s">
         <v>133</v>
       </c>
       <c r="N21" s="39"/>
@@ -6544,21 +6544,21 @@
       <c r="Q21" s="40"/>
     </row>
     <row r="22" spans="1:17">
-      <c r="A22" s="47" t="s">
+      <c r="A22" s="44" t="s">
         <v>87</v>
       </c>
       <c r="B22" s="39"/>
       <c r="C22" s="39"/>
       <c r="D22" s="39"/>
       <c r="E22" s="40"/>
-      <c r="G22" s="47" t="s">
+      <c r="G22" s="44" t="s">
         <v>87</v>
       </c>
       <c r="H22" s="39"/>
       <c r="I22" s="39"/>
       <c r="J22" s="39"/>
       <c r="K22" s="40"/>
-      <c r="M22" s="47" t="s">
+      <c r="M22" s="44" t="s">
         <v>87</v>
       </c>
       <c r="N22" s="39"/>
@@ -6866,21 +6866,21 @@
       <c r="Q29" s="30"/>
     </row>
     <row r="30" spans="1:17">
-      <c r="A30" s="47" t="s">
+      <c r="A30" s="44" t="s">
         <v>95</v>
       </c>
       <c r="B30" s="39"/>
       <c r="C30" s="39"/>
       <c r="D30" s="39"/>
       <c r="E30" s="40"/>
-      <c r="G30" s="47" t="s">
+      <c r="G30" s="44" t="s">
         <v>95</v>
       </c>
       <c r="H30" s="39"/>
       <c r="I30" s="39"/>
       <c r="J30" s="39"/>
       <c r="K30" s="40"/>
-      <c r="M30" s="47" t="s">
+      <c r="M30" s="44" t="s">
         <v>95</v>
       </c>
       <c r="N30" s="39"/>
@@ -7237,25 +7237,25 @@
       <c r="Q39" s="25"/>
     </row>
     <row r="41" spans="1:17">
-      <c r="A41" s="44" t="s">
+      <c r="A41" s="45" t="s">
         <v>135</v>
       </c>
-      <c r="B41" s="45"/>
-      <c r="C41" s="45"/>
+      <c r="B41" s="46"/>
+      <c r="C41" s="46"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
-      <c r="G41" s="44" t="s">
+      <c r="G41" s="45" t="s">
         <v>136</v>
       </c>
-      <c r="H41" s="45"/>
-      <c r="I41" s="45"/>
+      <c r="H41" s="46"/>
+      <c r="I41" s="46"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
-      <c r="M41" s="44" t="s">
+      <c r="M41" s="45" t="s">
         <v>137</v>
       </c>
-      <c r="N41" s="45"/>
-      <c r="O41" s="45"/>
+      <c r="N41" s="46"/>
+      <c r="O41" s="46"/>
       <c r="P41" s="1"/>
       <c r="Q41" s="1"/>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="B44" s="28">
         <f>(Inputs!$C$32*'Study Parameters'!$C$15 * 10^3) / 10^6</f>
-        <v>2857.5779999999995</v>
+        <v>3055.9589999999994</v>
       </c>
       <c r="C44" t="s">
         <v>97</v>
@@ -7339,7 +7339,7 @@
       </c>
       <c r="H44">
         <f>(Inputs!$C$32*'Study Parameters'!$C$15 * 10^3) / 10^6</f>
-        <v>2857.5779999999995</v>
+        <v>3055.9589999999994</v>
       </c>
       <c r="I44" t="s">
         <v>97</v>
@@ -7349,7 +7349,7 @@
       </c>
       <c r="N44">
         <f>(Inputs!$C$32*'Study Parameters'!$C$15 * 10^3) / 10^6</f>
-        <v>2857.5779999999995</v>
+        <v>3055.9589999999994</v>
       </c>
       <c r="O44" t="s">
         <v>97</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="B45" s="29">
         <f>B43-B17+B44</f>
-        <v>4157.9422379706102</v>
+        <v>4356.3232379706105</v>
       </c>
       <c r="C45" s="8" t="s">
         <v>97</v>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="H45" s="8">
         <f>H43-H17+H44</f>
-        <v>4150.0522379706108</v>
+        <v>4348.4332379706102</v>
       </c>
       <c r="I45" s="8" t="s">
         <v>97</v>
@@ -7381,7 +7381,7 @@
       </c>
       <c r="N45" s="26">
         <f>N43-N17+N44</f>
-        <v>4163.8622379706103</v>
+        <v>4362.2432379706106</v>
       </c>
       <c r="O45" s="8" t="s">
         <v>97</v>
@@ -7451,21 +7451,21 @@
       <c r="O48" s="6"/>
     </row>
     <row r="50" spans="1:15">
-      <c r="A50" s="44" t="s">
+      <c r="A50" s="45" t="s">
         <v>141</v>
       </c>
-      <c r="B50" s="45"/>
-      <c r="C50" s="45"/>
-      <c r="G50" s="44" t="s">
+      <c r="B50" s="46"/>
+      <c r="C50" s="46"/>
+      <c r="G50" s="45" t="s">
         <v>142</v>
       </c>
-      <c r="H50" s="45"/>
-      <c r="I50" s="45"/>
+      <c r="H50" s="46"/>
+      <c r="I50" s="46"/>
       <c r="M50" s="48" t="s">
         <v>143</v>
       </c>
-      <c r="N50" s="45"/>
-      <c r="O50" s="45"/>
+      <c r="N50" s="46"/>
+      <c r="O50" s="46"/>
     </row>
     <row r="51" spans="1:15">
       <c r="A51" t="s">
@@ -7537,7 +7537,7 @@
       </c>
       <c r="B53" s="28">
         <f>(Inputs!$C$33*'Study Parameters'!$C$15 * 10^3) / 10^6</f>
-        <v>1069.9199999999998</v>
+        <v>1165.7669999999998</v>
       </c>
       <c r="C53" t="s">
         <v>97</v>
@@ -7547,7 +7547,7 @@
       </c>
       <c r="H53" s="28">
         <f>(Inputs!$C$33*'Study Parameters'!$C$15 * 10^3) / 10^6</f>
-        <v>1069.9199999999998</v>
+        <v>1165.7669999999998</v>
       </c>
       <c r="I53" t="s">
         <v>97</v>
@@ -7557,7 +7557,7 @@
       </c>
       <c r="N53" s="28">
         <f>(Inputs!$C$33*'Study Parameters'!$C$15 * 10^3) / 10^6</f>
-        <v>1069.9199999999998</v>
+        <v>1165.7669999999998</v>
       </c>
       <c r="O53" t="s">
         <v>97</v>
@@ -7569,7 +7569,7 @@
       </c>
       <c r="B54" s="29">
         <f>B52-B37+B53</f>
-        <v>1346.5682106372774</v>
+        <v>1442.4152106372774</v>
       </c>
       <c r="C54" s="8" t="s">
         <v>97</v>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="H54" s="29">
         <f>H52-H37+H53</f>
-        <v>1349.7982106372774</v>
+        <v>1445.6452106372774</v>
       </c>
       <c r="I54" s="8" t="s">
         <v>97</v>
@@ -7589,7 +7589,7 @@
       </c>
       <c r="N54" s="29">
         <f>N52-N37+N53</f>
-        <v>1347.5682106372774</v>
+        <v>1443.4152106372774</v>
       </c>
       <c r="O54" s="8" t="s">
         <v>97</v>
@@ -7655,14 +7655,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="G21:K21"/>
-    <mergeCell ref="G2:K2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="G1:K1"/>
-    <mergeCell ref="G22:K22"/>
     <mergeCell ref="A50:C50"/>
     <mergeCell ref="M1:Q1"/>
     <mergeCell ref="M2:Q2"/>
@@ -7679,6 +7671,14 @@
     <mergeCell ref="G41:I41"/>
     <mergeCell ref="M50:O50"/>
     <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="G21:K21"/>
+    <mergeCell ref="G2:K2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="G1:K1"/>
+    <mergeCell ref="G22:K22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -16875,123 +16875,123 @@
       </c>
       <c r="C3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="D3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="E3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="F3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="G3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="H3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="I3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="J3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="K3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="L3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="M3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="N3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="O3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="P3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="Q3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="R3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="S3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="T3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="U3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="V3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="W3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="X3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="Y3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="Z3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="AA3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="AB3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="AC3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="AD3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="AE3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="AF3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
     </row>
     <row r="4" spans="1:32">
@@ -17132,123 +17132,123 @@
       </c>
       <c r="C5">
         <f>C3/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!C2) + C4</f>
-        <v>4404229700.9760323</v>
+        <v>4587915812.0871439</v>
       </c>
       <c r="D5">
         <f>D3/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!D2) + D4</f>
-        <v>4119048477.5212584</v>
+        <v>4289128210.0315466</v>
       </c>
       <c r="E5">
         <f>E3/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!E2) + E4</f>
-        <v>3854991789.137208</v>
+        <v>4012473022.9430304</v>
       </c>
       <c r="F5">
         <f>F3/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!F2) + F4</f>
-        <v>3610494855.4482718</v>
+        <v>3756310812.6758852</v>
       </c>
       <c r="G5">
         <f>G3/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!G2) + G4</f>
-        <v>3384108805.7362947</v>
+        <v>3519123580.9470482</v>
       </c>
       <c r="H5">
         <f>H3/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!H2) + H4</f>
-        <v>3174492093.040019</v>
+        <v>3299505773.7907171</v>
       </c>
       <c r="I5">
         <f>I3/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!I2) + I4</f>
-        <v>2980402544.2471714</v>
+        <v>3096155952.3496695</v>
       </c>
       <c r="J5">
         <f>J3/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!J2) + J4</f>
-        <v>2800689999.0686092</v>
+        <v>2907869080.6449957</v>
       </c>
       <c r="K5">
         <f>K3/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!K2) + K4</f>
-        <v>2634289494.273644</v>
+        <v>2733529384.6221504</v>
       </c>
       <c r="L5">
         <f>L3/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!L2) + L4</f>
-        <v>2480214952.7968245</v>
+        <v>2572103740.1565523</v>
       </c>
       <c r="M5">
         <f>M3/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!M2) + M4</f>
-        <v>2337553340.3182878</v>
+        <v>2422635550.8365545</v>
       </c>
       <c r="N5">
         <f>N3/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!N2) + N4</f>
-        <v>2205459254.6900129</v>
+        <v>2284239079.2439632</v>
       </c>
       <c r="O5">
         <f>O3/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!O2) + O4</f>
-        <v>2083149916.145314</v>
+        <v>2156094198.1397123</v>
       </c>
       <c r="P5">
         <f>P3/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!P2) + P4</f>
-        <v>1969900528.6039259</v>
+        <v>2037441530.4505913</v>
       </c>
       <c r="Q5">
         <f>Q3/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!Q2) + Q4</f>
-        <v>1865039984.5841224</v>
+        <v>1927577949.2569606</v>
       </c>
       <c r="R5">
         <f>R3/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!R2) + R4</f>
-        <v>1767946888.2694895</v>
+        <v>1825852411.1147103</v>
       </c>
       <c r="S5">
         <f>S3/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!S2) + S4</f>
-        <v>1678045873.163348</v>
+        <v>1731662098.0200338</v>
       </c>
       <c r="T5">
         <f>T3/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!T2) + T4</f>
-        <v>1594804192.5095131</v>
+        <v>1644448845.1545928</v>
       </c>
       <c r="U5">
         <f>U3/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!U2) + U4</f>
-        <v>1517728562.2744808</v>
+        <v>1563695833.242147</v>
       </c>
       <c r="V5">
         <f>V3/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!V2) + V4</f>
-        <v>1446362237.9827845</v>
+        <v>1488924525.9158087</v>
       </c>
       <c r="W5">
         <f>W3/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!W2) + W4</f>
-        <v>1380282308.0830655</v>
+        <v>1419691833.9469769</v>
       </c>
       <c r="X5">
         <f>X3/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!X2) + X4</f>
-        <v>1319097187.805548</v>
+        <v>1355587489.5313916</v>
       </c>
       <c r="Y5">
         <f>Y3/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!Y2) + Y4</f>
-        <v>1262444298.6596985</v>
+        <v>1296231615.0725169</v>
       </c>
       <c r="Z5">
         <f>Z3/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!Z2) + Z4</f>
-        <v>1209987919.8209488</v>
+        <v>1241272472.0550399</v>
       </c>
       <c r="AA5">
         <f>AA3/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AA2) + AA4</f>
-        <v>1161417198.6739583</v>
+        <v>1190384376.6684871</v>
       </c>
       <c r="AB5">
         <f>AB3/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AB2) + AB4</f>
-        <v>1116444308.7230415</v>
+        <v>1143265769.8290868</v>
       </c>
       <c r="AC5">
         <f>AC3/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AC2) + AC4</f>
-        <v>1074802743.9536738</v>
+        <v>1099637430.1629748</v>
       </c>
       <c r="AD5">
         <f>AD3/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AD2) + AD4</f>
-        <v>1036245739.5375928</v>
+        <v>1059240819.3610196</v>
       </c>
       <c r="AE5">
         <f>AE3/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AE2) + AE4</f>
-        <v>1000544809.5227028</v>
+        <v>1021836550.09995</v>
       </c>
       <c r="AF5">
         <f>AF3/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AF2) + AF4</f>
-        <v>967488392.84224916</v>
+        <v>987202967.45081139</v>
       </c>
     </row>
     <row r="6" spans="1:32">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="B9">
         <f>SUM(B5:AF5) / SUM(B7:AF7)</f>
-        <v>7.0437610212511137</v>
+        <v>7.2917372712511144</v>
       </c>
     </row>
     <row r="11" spans="1:32">
@@ -17629,123 +17629,123 @@
       </c>
       <c r="C13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="D13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="E13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="F13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="G13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="H13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="I13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="J13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="K13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="L13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="M13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="N13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="O13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="P13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="Q13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="R13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="S13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="T13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="U13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="V13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="W13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="X13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="Y13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="Z13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="AA13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="AB13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="AC13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="AD13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="AE13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="AF13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
     </row>
     <row r="14" spans="1:32">
@@ -17885,123 +17885,123 @@
       </c>
       <c r="C15">
         <f>C13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!C12) +C14</f>
-        <v>1578681708.3915875</v>
+        <v>1667428930.6138098</v>
       </c>
       <c r="D15">
         <f>D13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!D12) +D14</f>
-        <v>1486324492.2984958</v>
+        <v>1568497846.2079608</v>
       </c>
       <c r="E15">
         <f>E13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!E12) +E14</f>
-        <v>1400808551.471559</v>
+        <v>1476894990.2766192</v>
       </c>
       <c r="F15">
         <f>F13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!F12) +F14</f>
-        <v>1321627124.7799506</v>
+        <v>1392077531.0809324</v>
       </c>
       <c r="G15">
         <f>G13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!G12) +G14</f>
-        <v>1248310988.9543877</v>
+        <v>1313542846.6404819</v>
       </c>
       <c r="H15">
         <f>H13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!H12) +H14</f>
-        <v>1180425678.0047922</v>
+        <v>1240825546.232657</v>
       </c>
       <c r="I15">
         <f>I13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!I12) +I14</f>
-        <v>1117568908.6070185</v>
+        <v>1173494712.5217085</v>
       </c>
       <c r="J15">
         <f>J13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!J12) +J14</f>
-        <v>1059368196.2016727</v>
+        <v>1111151347.9745336</v>
       </c>
       <c r="K15">
         <f>K13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!K12) +K14</f>
-        <v>1005478647.6782043</v>
+        <v>1053426010.4308532</v>
       </c>
       <c r="L15">
         <f>L13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!L12) +L14</f>
-        <v>955580917.56388164</v>
+        <v>999976623.81633437</v>
       </c>
       <c r="M15">
         <f>M13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!M12) +M14</f>
-        <v>909379315.60617554</v>
+        <v>950486451.02511322</v>
       </c>
       <c r="N15">
         <f>N13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!N12) +N14</f>
-        <v>866600054.53422546</v>
+        <v>904662216.95916772</v>
       </c>
       <c r="O15">
         <f>O13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!O12) +O14</f>
-        <v>826989627.61575317</v>
+        <v>862232370.60181081</v>
       </c>
       <c r="P15">
         <f>P13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!P12) +P14</f>
-        <v>790313306.39494538</v>
+        <v>822945475.82648027</v>
       </c>
       <c r="Q15">
         <f>Q13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!Q12) +Q14</f>
-        <v>756353749.70901227</v>
+        <v>786568721.4048779</v>
       </c>
       <c r="R15">
         <f>R13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!R12) +R14</f>
-        <v>724909715.74055576</v>
+        <v>752886541.38487577</v>
       </c>
       <c r="S15">
         <f>S13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!S12) +S14</f>
-        <v>695794869.4734664</v>
+        <v>721699337.66265154</v>
       </c>
       <c r="T15">
         <f>T13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!T12) +T14</f>
-        <v>668836678.4854207</v>
+        <v>692822297.17911065</v>
       </c>
       <c r="U15">
         <f>U13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!U12) +U14</f>
-        <v>643875390.53352642</v>
+        <v>666084296.73138762</v>
       </c>
       <c r="V15">
         <f>V13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!V12) +V14</f>
-        <v>620763086.87436521</v>
+        <v>641326888.9094218</v>
       </c>
       <c r="W15">
         <f>W13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!W12) +W14</f>
-        <v>599362805.70847511</v>
+        <v>618403363.14834237</v>
       </c>
       <c r="X15">
         <f>X13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!X12) +X14</f>
-        <v>579547730.55487323</v>
+        <v>597177876.332528</v>
       </c>
       <c r="Y15">
         <f>Y13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!Y12) +Y14</f>
-        <v>561200438.74598253</v>
+        <v>577524647.79936659</v>
       </c>
       <c r="Z15">
         <f>Z13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!Z12) +Z14</f>
-        <v>544212205.58960223</v>
+        <v>559327213.97236538</v>
       </c>
       <c r="AA15">
         <f>AA13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AA12) +AA14</f>
-        <v>528482360.07443535</v>
+        <v>542477738.20662332</v>
       </c>
       <c r="AB15">
         <f>AB13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AB12) +AB14</f>
-        <v>513917688.30113268</v>
+        <v>526876371.75686234</v>
       </c>
       <c r="AC15">
         <f>AC13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AC12) +AC14</f>
-        <v>500431881.10363019</v>
+        <v>512430662.08115768</v>
       </c>
       <c r="AD15">
         <f>AD13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AD12) +AD14</f>
-        <v>487945022.58742422</v>
+        <v>499055004.9740237</v>
       </c>
       <c r="AE15">
         <f>AE13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AE12) +AE14</f>
-        <v>476383116.55390012</v>
+        <v>486670137.282233</v>
       </c>
       <c r="AF15">
         <f>AF13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AF12) +AF14</f>
-        <v>465677648.00434083</v>
+        <v>475202667.1972416</v>
       </c>
     </row>
     <row r="16" spans="1:32">
@@ -18266,7 +18266,7 @@
       </c>
       <c r="B19">
         <f>SUM(B15:AF15) / SUM(B17:AF17)</f>
-        <v>2.7886431036926567</v>
+        <v>2.9084518536926556</v>
       </c>
     </row>
     <row r="21" spans="1:32" s="24" customFormat="1"/>
@@ -18382,123 +18382,123 @@
       </c>
       <c r="C25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="D25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="E25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="F25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="G25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="H25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="I25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="J25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="K25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="L25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="M25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="N25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="O25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="P25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="Q25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="R25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="S25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="T25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="U25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="V25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="W25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="X25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="Y25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="Z25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="AA25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="AB25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="AC25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="AD25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="AE25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="AF25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
     </row>
     <row r="26" spans="1:32">
@@ -18639,123 +18639,123 @@
       </c>
       <c r="C27">
         <f>C25/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!C24) + C26</f>
-        <v>4282869720.95122</v>
+        <v>4466555832.0623312</v>
       </c>
       <c r="D27">
         <f>D25/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!D24) + D26</f>
-        <v>3998229649.75982</v>
+        <v>4168309382.2701082</v>
       </c>
       <c r="E27">
         <f>E25/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!E24) + E26</f>
-        <v>3734674028.2863016</v>
+        <v>3892155262.0921235</v>
       </c>
       <c r="F27">
         <f>F25/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!F24) + F26</f>
-        <v>3490641045.4404507</v>
+        <v>3636457002.6680641</v>
       </c>
       <c r="G27">
         <f>G25/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!G24) + G26</f>
-        <v>3264684579.8424411</v>
+        <v>3399699355.053194</v>
       </c>
       <c r="H27">
         <f>H25/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!H24) + H26</f>
-        <v>3055465630.2146544</v>
+        <v>3180479310.9653516</v>
       </c>
       <c r="I27">
         <f>I25/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!I24) + I26</f>
-        <v>2861744380.5592961</v>
+        <v>2977497788.6617937</v>
       </c>
       <c r="J27">
         <f>J25/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!J24) + J26</f>
-        <v>2682372853.1006312</v>
+        <v>2789551934.6770177</v>
       </c>
       <c r="K27">
         <f>K25/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!K24) + K26</f>
-        <v>2516288105.4537191</v>
+        <v>2615527995.8022251</v>
       </c>
       <c r="L27">
         <f>L25/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!L24) + L26</f>
-        <v>2362505931.7065787</v>
+        <v>2454394719.0663066</v>
       </c>
       <c r="M27">
         <f>M25/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!M24) + M26</f>
-        <v>2220115030.0888557</v>
+        <v>2305197240.6071224</v>
       </c>
       <c r="N27">
         <f>N25/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!N24) + N26</f>
-        <v>2088271602.6650386</v>
+        <v>2167051427.2189889</v>
       </c>
       <c r="O27">
         <f>O25/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!O24) + O26</f>
-        <v>1966194355.0503929</v>
+        <v>2039138637.0447912</v>
       </c>
       <c r="P27">
         <f>P25/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!P24) + P26</f>
-        <v>1853159866.5183132</v>
+        <v>1920700868.3649786</v>
       </c>
       <c r="Q27">
         <f>Q25/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!Q24) + Q26</f>
-        <v>1748498303.0626841</v>
+        <v>1811036267.7355223</v>
       </c>
       <c r="R27">
         <f>R25/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!R24) + R26</f>
-        <v>1651589448.0111759</v>
+        <v>1709494970.8563964</v>
       </c>
       <c r="S27">
         <f>S25/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!S24) + S26</f>
-        <v>1561859026.6671865</v>
+        <v>1615475251.5238721</v>
       </c>
       <c r="T27">
         <f>T25/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!T24) + T26</f>
-        <v>1478775303.2005298</v>
+        <v>1528419955.8456092</v>
       </c>
       <c r="U27">
         <f>U25/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!U24) + U26</f>
-        <v>1401845929.6202922</v>
+        <v>1447813200.5879581</v>
       </c>
       <c r="V27">
         <f>V25/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!V24) + V26</f>
-        <v>1330615028.157109</v>
+        <v>1373177316.0901332</v>
       </c>
       <c r="W27">
         <f>W25/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!W24) + W26</f>
-        <v>1264660489.7652729</v>
+        <v>1304070015.6291842</v>
       </c>
       <c r="X27">
         <f>X25/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!X24) + X26</f>
-        <v>1203591472.735795</v>
+        <v>1240081774.4616387</v>
       </c>
       <c r="Y27">
         <f>Y25/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!Y24) + Y26</f>
-        <v>1147046086.5973895</v>
+        <v>1180833403.0102077</v>
       </c>
       <c r="Z27">
         <f>Z25/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!Z24) + Z26</f>
-        <v>1094689247.5803475</v>
+        <v>1125973799.8144383</v>
       </c>
       <c r="AA27">
         <f>AA25/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AA24) + AA26</f>
-        <v>1046210692.934938</v>
+        <v>1075177870.9294667</v>
       </c>
       <c r="AB27">
         <f>AB25/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AB24) + AB26</f>
-        <v>1001323142.3373368</v>
+        <v>1028144603.4433819</v>
       </c>
       <c r="AC27">
         <f>AC25/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AC24) + AC26</f>
-        <v>959760595.48770595</v>
+        <v>984595281.69700706</v>
       </c>
       <c r="AD27">
         <f>AD25/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AD24) + AD26</f>
-        <v>921276755.81212199</v>
+        <v>944271835.63554883</v>
       </c>
       <c r="AE27">
         <f>AE25/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AE24) + AE26</f>
-        <v>885643570.92732191</v>
+        <v>906935311.50456905</v>
       </c>
       <c r="AF27">
         <f>AF25/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AF24) + AF26</f>
-        <v>852649881.21917367</v>
+        <v>872364455.82773578</v>
       </c>
     </row>
     <row r="28" spans="1:32">
@@ -19021,7 +19021,7 @@
       </c>
       <c r="B31">
         <f>SUM(B27:AF27) / SUM(B29:AF29)</f>
-        <v>6.6539799540486122</v>
+        <v>6.9019562040486138</v>
       </c>
     </row>
     <row r="33" spans="1:32">
@@ -19136,123 +19136,123 @@
       </c>
       <c r="C36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="D36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="E36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="F36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="G36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="H36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="I36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="J36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="K36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="L36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="M36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="N36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="O36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="P36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="Q36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="R36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="S36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="T36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="U36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="V36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="W36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="X36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="Y36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="Z36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="AA36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="AB36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="AC36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="AD36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="AE36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="AF36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
     </row>
     <row r="37" spans="1:32">
@@ -19393,123 +19393,123 @@
       </c>
       <c r="C38">
         <f>C36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!C35) + C37</f>
-        <v>1584692581.8674955</v>
+        <v>1673439804.0897179</v>
       </c>
       <c r="D38">
         <f>D36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!D35) + D37</f>
-        <v>1492113829.4232378</v>
+        <v>1574287183.3327029</v>
       </c>
       <c r="E38">
         <f>E36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!E35) + E37</f>
-        <v>1406392762.3452215</v>
+        <v>1482479201.1502817</v>
       </c>
       <c r="F38">
         <f>F36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!F35) + F37</f>
-        <v>1327021403.9396505</v>
+        <v>1397471810.2406321</v>
       </c>
       <c r="G38">
         <f>G36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!G35) + G37</f>
-        <v>1253529405.4159741</v>
+        <v>1318761263.1020679</v>
       </c>
       <c r="H38">
         <f>H36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!H35) + H37</f>
-        <v>1185481258.6347919</v>
+        <v>1245881126.8626566</v>
       </c>
       <c r="I38">
         <f>I36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!I35) + I37</f>
-        <v>1122473715.3188825</v>
+        <v>1178399519.2335722</v>
       </c>
       <c r="J38">
         <f>J36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!J35) + J37</f>
-        <v>1064133397.4337814</v>
+        <v>1115916549.2066422</v>
       </c>
       <c r="K38">
         <f>K36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!K35) + K37</f>
-        <v>1010114584.5772061</v>
+        <v>1058061947.3298551</v>
       </c>
       <c r="L38">
         <f>L36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!L35) + L37</f>
-        <v>960097165.26556242</v>
+        <v>1004492871.5180151</v>
       </c>
       <c r="M38">
         <f>M36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!M35) + M37</f>
-        <v>913784739.97700346</v>
+        <v>954891875.39594126</v>
       </c>
       <c r="N38">
         <f>N36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!N35) + N37</f>
-        <v>870902864.7098192</v>
+        <v>908965027.13476157</v>
       </c>
       <c r="O38">
         <f>O36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!O35) + O37</f>
-        <v>831197424.64761162</v>
+        <v>866440167.63366938</v>
       </c>
       <c r="P38">
         <f>P36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!P35) + P37</f>
-        <v>794433128.2937156</v>
+        <v>827065297.72525048</v>
       </c>
       <c r="Q38">
         <f>Q36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!Q35) + Q37</f>
-        <v>760392113.15121937</v>
+        <v>790607084.847085</v>
       </c>
       <c r="R38">
         <f>R36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!R35) + R37</f>
-        <v>728872654.68594503</v>
+        <v>756849480.33026516</v>
       </c>
       <c r="S38">
         <f>S36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!S35) + S37</f>
-        <v>699687970.92180228</v>
+        <v>725592439.11098742</v>
       </c>
       <c r="T38">
         <f>T36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!T35) + T37</f>
-        <v>672665115.58463287</v>
+        <v>696650734.27832294</v>
       </c>
       <c r="U38">
         <f>U36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!U35) + U37</f>
-        <v>647643953.23540199</v>
+        <v>669852859.43326306</v>
       </c>
       <c r="V38">
         <f>V36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!V35) + V37</f>
-        <v>624476210.31944752</v>
+        <v>645040012.35450411</v>
       </c>
       <c r="W38">
         <f>W36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!W35) + W37</f>
-        <v>603024596.50837862</v>
+        <v>622065153.94824576</v>
       </c>
       <c r="X38">
         <f>X36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!X35) + X37</f>
-        <v>583161991.1277591</v>
+        <v>600792136.90541399</v>
       </c>
       <c r="Y38">
         <f>Y36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!Y35) + Y37</f>
-        <v>564770689.84940779</v>
+        <v>581094898.90279198</v>
       </c>
       <c r="Z38">
         <f>Z36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!Z35) + Z37</f>
-        <v>547741707.18426776</v>
+        <v>562856715.56703079</v>
       </c>
       <c r="AA38">
         <f>AA36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AA35) + AA37</f>
-        <v>531974130.64247131</v>
+        <v>545969508.7746594</v>
       </c>
       <c r="AB38">
         <f>AB36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AB35) + AB37</f>
-        <v>517374522.73340058</v>
+        <v>530333206.18913031</v>
       </c>
       <c r="AC38">
         <f>AC36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AC35) + AC37</f>
-        <v>503856367.26203883</v>
+        <v>515855148.23956633</v>
       </c>
       <c r="AD38">
         <f>AD36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AD35) + AD37</f>
-        <v>491339556.64040756</v>
+        <v>502449539.02700704</v>
       </c>
       <c r="AE38">
         <f>AE36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AE35) + AE37</f>
-        <v>479749917.17593414</v>
+        <v>490036937.90426701</v>
       </c>
       <c r="AF38">
         <f>AF36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AF35) + AF37</f>
-        <v>469018769.52364391</v>
+        <v>478543788.71654475</v>
       </c>
     </row>
     <row r="39" spans="1:32">
@@ -19775,7 +19775,7 @@
       </c>
       <c r="B42">
         <f>SUM(B38:AF38) / SUM(B40:AF40)</f>
-        <v>2.8027407526684223</v>
+        <v>2.9225495026684225</v>
       </c>
     </row>
     <row r="44" spans="1:32" s="24" customFormat="1"/>
@@ -19891,123 +19891,123 @@
       </c>
       <c r="C49">
         <f>'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="D49">
         <f>'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="E49">
         <f>'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="F49">
         <f>'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="G49">
         <f>'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="H49">
         <f>'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="I49">
         <f>'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="J49">
         <f>'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="K49">
         <f>'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="L49">
         <f>'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="M49">
         <f>'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="N49">
         <f>'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="O49">
         <f>'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="P49">
         <f>'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="Q49">
         <f>'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="R49">
         <f>'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="S49">
         <f>'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="T49">
         <f>'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="U49">
         <f>'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="V49">
         <f>'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="W49">
         <f>'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="X49">
         <f>'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="Y49">
         <f>'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="Z49">
         <f>'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="AA49">
         <f>'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="AB49">
         <f>'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="AC49">
         <f>'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="AD49">
         <f>'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="AE49">
         <f>'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="AF49">
         <f>'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
     </row>
     <row r="50" spans="1:32">
@@ -20147,123 +20147,123 @@
       </c>
       <c r="C51">
         <f>C49/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!C48) + C50</f>
-        <v>4424278881.5330267</v>
+        <v>4607964992.6441383</v>
       </c>
       <c r="D51">
         <f>D49/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!D48) + D50</f>
-        <v>4138691622.4129577</v>
+        <v>4308771354.9232464</v>
       </c>
       <c r="E51">
         <f>E49/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!E48) + E50</f>
-        <v>3874258975.0795598</v>
+        <v>4031740208.8853827</v>
       </c>
       <c r="F51">
         <f>F49/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!F48) + F50</f>
-        <v>3629413931.2523398</v>
+        <v>3775229888.4799533</v>
       </c>
       <c r="G51">
         <f>G49/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!G48) + G50</f>
-        <v>3402705557.3382473</v>
+        <v>3537720332.5490007</v>
       </c>
       <c r="H51">
         <f>H49/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!H48) + H50</f>
-        <v>3192790396.3066797</v>
+        <v>3317804077.0573773</v>
       </c>
       <c r="I51">
         <f>I49/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!I48) + I50</f>
-        <v>2998424506.462636</v>
+        <v>3114177914.565134</v>
       </c>
       <c r="J51">
         <f>J49/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!J48) + J50</f>
-        <v>2818456089.9403734</v>
+        <v>2925635171.5167603</v>
       </c>
       <c r="K51">
         <f>K49/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!K48) + K50</f>
-        <v>2651818667.2345748</v>
+        <v>2751058557.5830812</v>
       </c>
       <c r="L51">
         <f>L49/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!L48) + L50</f>
-        <v>2497524757.3217983</v>
+        <v>2589413544.6815262</v>
       </c>
       <c r="M51">
         <f>M49/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!M48) + M50</f>
-        <v>2354660025.9210792</v>
+        <v>2439742236.4393458</v>
       </c>
       <c r="N51">
         <f>N49/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!N48) + N50</f>
-        <v>2222377867.2167096</v>
+        <v>2301157691.7706604</v>
       </c>
       <c r="O51">
         <f>O49/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!O48) + O50</f>
-        <v>2099894386.9348862</v>
+        <v>2172838668.929285</v>
       </c>
       <c r="P51">
         <f>P49/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!P48) + P50</f>
-        <v>1986483757.0443084</v>
+        <v>2054024758.890974</v>
       </c>
       <c r="Q51">
         <f>Q49/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!Q48) + Q50</f>
-        <v>1881473914.5530331</v>
+        <v>1944011879.2258716</v>
       </c>
       <c r="R51">
         <f>R49/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!R48) + R50</f>
-        <v>1784242578.9129634</v>
+        <v>1842148101.7581842</v>
       </c>
       <c r="S51">
         <f>S49/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!S48) + S50</f>
-        <v>1694213564.4314172</v>
+        <v>1747829789.2881031</v>
       </c>
       <c r="T51">
         <f>T49/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!T48) + T50</f>
-        <v>1610853365.8373933</v>
+        <v>1660498018.4824727</v>
       </c>
       <c r="U51">
         <f>U49/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!U48) + U50</f>
-        <v>1533667996.7688522</v>
+        <v>1579635267.7365184</v>
       </c>
       <c r="V51">
         <f>V49/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!V48) + V50</f>
-        <v>1462200062.4461293</v>
+        <v>1504762350.3791535</v>
       </c>
       <c r="W51">
         <f>W49/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!W48) + W50</f>
-        <v>1396026049.1843486</v>
+        <v>1435435575.04826</v>
       </c>
       <c r="X51">
         <f>X49/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!X48) + X50</f>
-        <v>1334753814.6826999</v>
+        <v>1371244116.4085436</v>
       </c>
       <c r="Y51">
         <f>Y49/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!Y48) + Y50</f>
-        <v>1278020264.2182102</v>
+        <v>1311807580.6310287</v>
       </c>
       <c r="Z51">
         <f>Z49/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!Z48) + Z50</f>
-        <v>1225489198.9733126</v>
+        <v>1256773751.2074037</v>
       </c>
       <c r="AA51">
         <f>AA49/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AA48) + AA50</f>
-        <v>1176849323.7465553</v>
+        <v>1205816501.7410841</v>
       </c>
       <c r="AB51">
         <f>AB49/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AB48) + AB50</f>
-        <v>1131812402.240299</v>
+        <v>1158633863.346344</v>
       </c>
       <c r="AC51">
         <f>AC49/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AC48) + AC50</f>
-        <v>1090111548.9937651</v>
+        <v>1114946235.2030661</v>
       </c>
       <c r="AD51">
         <f>AD49/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AD48) + AD50</f>
-        <v>1051499647.8395671</v>
+        <v>1074494727.6629939</v>
       </c>
       <c r="AE51">
         <f>AE49/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AE48) + AE50</f>
-        <v>1015747887.5116059</v>
+        <v>1037039628.088853</v>
       </c>
       <c r="AF51">
         <f>AF49/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AF48) + AF50</f>
-        <v>982644405.72645664</v>
+        <v>1002358980.3350189</v>
       </c>
     </row>
     <row r="52" spans="1:32">
@@ -20528,7 +20528,7 @@
       </c>
       <c r="B55">
         <f>SUM(B51:AF51) / SUM(B53:AF53)</f>
-        <v>7.0996864457224591</v>
+        <v>7.3476626957224616</v>
       </c>
     </row>
     <row r="57" spans="1:32">
@@ -20643,123 +20643,123 @@
       </c>
       <c r="C59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="D59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="E59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="F59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="G59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="H59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="I59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="J59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="K59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="L59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="M59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="N59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="O59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="P59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="Q59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="R59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="S59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="T59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="U59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="V59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="W59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="X59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="Y59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="Z59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="AA59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="AB59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="AC59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="AD59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="AE59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="AF59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
     </row>
     <row r="60" spans="1:32">
@@ -20899,123 +20899,123 @@
       </c>
       <c r="C61">
         <f>C59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!C58) + C60</f>
-        <v>1578808187.417028</v>
+        <v>1667555409.63925</v>
       </c>
       <c r="D61">
         <f>D59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!D58) + D60</f>
-        <v>1486382384.218312</v>
+        <v>1568555738.1277771</v>
       </c>
       <c r="E61">
         <f>E59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!E58) + E60</f>
-        <v>1400802936.8120937</v>
+        <v>1476889375.6171539</v>
       </c>
       <c r="F61">
         <f>F59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!F58) + F60</f>
-        <v>1321562707.7322617</v>
+        <v>1392013114.0332434</v>
       </c>
       <c r="G61">
         <f>G59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!G58) + G60</f>
-        <v>1248192125.250936</v>
+        <v>1313423982.9370301</v>
       </c>
       <c r="H61">
         <f>H59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!H58) + H60</f>
-        <v>1180256400.7311897</v>
+        <v>1240656268.9590547</v>
       </c>
       <c r="I61">
         <f>I59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!I58) + I60</f>
-        <v>1117352952.1017952</v>
+        <v>1173278756.016485</v>
       </c>
       <c r="J61">
         <f>J59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!J58) + J60</f>
-        <v>1059109018.1856892</v>
+        <v>1110892169.95855</v>
       </c>
       <c r="K61">
         <f>K59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!K58) + K60</f>
-        <v>1005179449.7448502</v>
+        <v>1053126812.4974992</v>
       </c>
       <c r="L61">
         <f>L59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!L58) + L60</f>
-        <v>955244664.15148091</v>
+        <v>999640370.40393353</v>
       </c>
       <c r="M61">
         <f>M59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!M58) + M60</f>
-        <v>909008751.56502771</v>
+        <v>950115886.9839654</v>
       </c>
       <c r="N61">
         <f>N59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!N58) + N60</f>
-        <v>866197721.39238596</v>
+        <v>904259883.81732821</v>
       </c>
       <c r="O61">
         <f>O59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!O58) + O60</f>
-        <v>826557878.63993979</v>
+        <v>861800621.62599754</v>
       </c>
       <c r="P61">
         <f>P59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!P58) + P60</f>
-        <v>789854320.53582311</v>
+        <v>822486489.96735787</v>
       </c>
       <c r="Q61">
         <f>Q59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!Q58) + Q60</f>
-        <v>755869544.5134927</v>
+        <v>786084516.20935833</v>
       </c>
       <c r="R61">
         <f>R59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!R58) + R60</f>
-        <v>724402159.30763125</v>
+        <v>752378984.95195138</v>
       </c>
       <c r="S61">
         <f>S59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!S58) + S60</f>
-        <v>695265691.52442622</v>
+        <v>721170159.7136116</v>
       </c>
       <c r="T61">
         <f>T59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!T58) + T60</f>
-        <v>668287480.61405134</v>
+        <v>692273099.30774128</v>
       </c>
       <c r="U61">
         <f>U59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!U58) + U60</f>
-        <v>643307655.69703734</v>
+        <v>665516561.89489841</v>
       </c>
       <c r="V61">
         <f>V59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!V58) + V60</f>
-        <v>620178188.18128371</v>
+        <v>640741990.21634042</v>
       </c>
       <c r="W61">
         <f>W59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!W58) + W60</f>
-        <v>598762014.55558598</v>
+        <v>617802571.99545324</v>
       </c>
       <c r="X61">
         <f>X59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!X58) + X60</f>
-        <v>578932224.1614213</v>
+        <v>596562369.93907619</v>
       </c>
       <c r="Y61">
         <f>Y59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!Y58) + Y60</f>
-        <v>560571307.12978745</v>
+        <v>576895516.18317151</v>
       </c>
       <c r="Z61">
         <f>Z59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!Z58) + Z60</f>
-        <v>543570458.02642274</v>
+        <v>558685466.40918589</v>
       </c>
       <c r="AA61">
         <f>AA59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AA58) + AA60</f>
-        <v>527828931.07886279</v>
+        <v>541824309.21105087</v>
       </c>
       <c r="AB61">
         <f>AB59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AB58) + AB60</f>
-        <v>513253443.16445553</v>
+        <v>526212126.62018514</v>
       </c>
       <c r="AC61">
         <f>AC59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AC58) + AC60</f>
-        <v>499757621.02148575</v>
+        <v>511756401.99901319</v>
       </c>
       <c r="AD61">
         <f>AD59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AD58) + AD60</f>
-        <v>487261489.40762484</v>
+        <v>498371471.79422438</v>
       </c>
       <c r="AE61">
         <f>AE59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AE58) + AE60</f>
-        <v>475690997.17256844</v>
+        <v>485978017.90090132</v>
       </c>
       <c r="AF61">
         <f>AF59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AF58) + AF60</f>
-        <v>464977578.43640518</v>
+        <v>474502597.62930596</v>
       </c>
     </row>
     <row r="62" spans="1:32">
@@ -21280,7 +21280,7 @@
       </c>
       <c r="B65">
         <f>SUM(B61:AF61) / SUM(B63:AF63)</f>
-        <v>2.7872301230814234</v>
+        <v>2.9070388730814232</v>
       </c>
     </row>
   </sheetData>
@@ -21410,123 +21410,123 @@
       </c>
       <c r="C3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="D3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="E3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="F3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="G3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="H3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="I3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="J3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="K3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="L3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="M3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="N3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="O3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="P3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="Q3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="R3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="S3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="T3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="U3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="V3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="W3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="X3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="Y3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="Z3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="AA3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="AB3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="AC3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="AD3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="AE3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
       <c r="AF3">
         <f>'Cost Components'!$B$45 * 10^6</f>
-        <v>4157942237.9706101</v>
+        <v>4356323237.9706106</v>
       </c>
     </row>
     <row r="4" spans="1:32">
@@ -21667,123 +21667,123 @@
       </c>
       <c r="C5">
         <f>C3/((1+'Cost Components'!$B$46)^'MFSP Baseline'!C2)+C4</f>
-        <v>4388786483.1155119</v>
+        <v>4574189286.8538294</v>
       </c>
       <c r="D5">
         <f>D3/((1+'Cost Components'!$B$46)^'MFSP Baseline'!D2)+D4</f>
-        <v>4134566938.4758549</v>
+        <v>4307840586.8294239</v>
       </c>
       <c r="E5">
         <f>E3/((1+'Cost Components'!$B$46)^'MFSP Baseline'!E2)+E4</f>
-        <v>3896978578.9995403</v>
+        <v>4058916568.1150246</v>
       </c>
       <c r="F5">
         <f>F3/((1+'Cost Components'!$B$46)^'MFSP Baseline'!F2)+F4</f>
-        <v>3674933383.2272844</v>
+        <v>3826277298.2884846</v>
       </c>
       <c r="G5">
         <f>G3/((1+'Cost Components'!$B$46)^'MFSP Baseline'!G2)+G4</f>
-        <v>3467414508.6737728</v>
+        <v>3608857419.9459229</v>
       </c>
       <c r="H5">
         <f>H3/((1+'Cost Components'!$B$46)^'MFSP Baseline'!H2)+H4</f>
-        <v>3273471635.2592773</v>
+        <v>3405661271.9622211</v>
       </c>
       <c r="I5">
         <f>I3/((1+'Cost Components'!$B$46)^'MFSP Baseline'!I2)+I4</f>
-        <v>3092216613.3765707</v>
+        <v>3215758329.9213781</v>
       </c>
       <c r="J5">
         <f>J3/((1+'Cost Components'!$B$46)^'MFSP Baseline'!J2)+J4</f>
-        <v>2922819396.6637611</v>
+        <v>3038278944.8364782</v>
       </c>
       <c r="K5">
         <f>K3/((1+'Cost Components'!$B$46)^'MFSP Baseline'!K2)+K4</f>
-        <v>2764504240.8573961</v>
+        <v>2872410360.6449823</v>
       </c>
       <c r="L5">
         <f>L3/((1+'Cost Components'!$B$46)^'MFSP Baseline'!L2)+L4</f>
-        <v>2616546151.318738</v>
+        <v>2717392992.2417154</v>
       </c>
       <c r="M5">
         <f>M3/((1+'Cost Components'!$B$46)^'MFSP Baseline'!M2)+M4</f>
-        <v>2478267562.9648514</v>
+        <v>2572516947.0050173</v>
       </c>
       <c r="N5">
         <f>N3/((1+'Cost Components'!$B$46)^'MFSP Baseline'!N2)+N4</f>
-        <v>2349035237.4004722</v>
+        <v>2437118773.8866086</v>
       </c>
       <c r="O5">
         <f>O3/((1+'Cost Components'!$B$46)^'MFSP Baseline'!O2)+O4</f>
-        <v>2228257363.0412388</v>
+        <v>2310578425.177815</v>
       </c>
       <c r="P5">
         <f>P3/((1+'Cost Components'!$B$46)^'MFSP Baseline'!P2)+P4</f>
-        <v>2115380844.9484973</v>
+        <v>2192316417.0387554</v>
       </c>
       <c r="Q5">
         <f>Q3/((1+'Cost Components'!$B$46)^'MFSP Baseline'!Q2)+Q4</f>
-        <v>2009888771.9646266</v>
+        <v>2081791175.7872977</v>
       </c>
       <c r="R5">
         <f>R3/((1+'Cost Components'!$B$46)^'MFSP Baseline'!R2)+R4</f>
-        <v>1911298049.5497947</v>
+        <v>1978496557.7952816</v>
       </c>
       <c r="S5">
         <f>S3/((1+'Cost Components'!$B$46)^'MFSP Baseline'!S2)+S4</f>
-        <v>1819157187.4798579</v>
+        <v>1881959531.6345186</v>
       </c>
       <c r="T5">
         <f>T3/((1+'Cost Components'!$B$46)^'MFSP Baseline'!T2)+T4</f>
-        <v>1733044232.2743096</v>
+        <v>1791738011.8581047</v>
       </c>
       <c r="U5">
         <f>U3/((1+'Cost Components'!$B$46)^'MFSP Baseline'!U2)+U4</f>
-        <v>1652564834.8859465</v>
+        <v>1707418834.4969702</v>
       </c>
       <c r="V5">
         <f>V3/((1+'Cost Components'!$B$46)^'MFSP Baseline'!V2)+V4</f>
-        <v>1577350444.8033645</v>
+        <v>1628615865.0005827</v>
       </c>
       <c r="W5">
         <f>W3/((1+'Cost Components'!$B$46)^'MFSP Baseline'!W2)+W4</f>
-        <v>1507056622.2962785</v>
+        <v>1554968229.9572301</v>
       </c>
       <c r="X5">
         <f>X3/((1+'Cost Components'!$B$46)^'MFSP Baseline'!X2)+X4</f>
-        <v>1441361461.0747027</v>
+        <v>1486138664.4961526</v>
       </c>
       <c r="Y5">
         <f>Y3/((1+'Cost Components'!$B$46)^'MFSP Baseline'!Y2)+Y4</f>
-        <v>1379964114.1386504</v>
+        <v>1421811967.8035569</v>
       </c>
       <c r="Z5">
         <f>Z3/((1+'Cost Components'!$B$46)^'MFSP Baseline'!Z2)+Z4</f>
-        <v>1322583416.0675735</v>
+        <v>1361693559.679636</v>
       </c>
       <c r="AA5">
         <f>AA3/((1+'Cost Components'!$B$46)^'MFSP Baseline'!AA2)+AA4</f>
-        <v>1268956595.4403992</v>
+        <v>1305508131.5264385</v>
       </c>
       <c r="AB5">
         <f>AB3/((1+'Cost Components'!$B$46)^'MFSP Baseline'!AB2)+AB4</f>
-        <v>1218838071.4897685</v>
+        <v>1252998385.588871</v>
       </c>
       <c r="AC5">
         <f>AC3/((1+'Cost Components'!$B$46)^'MFSP Baseline'!AC2)+AC4</f>
-        <v>1171998329.4798336</v>
+        <v>1203923856.6752563</v>
       </c>
       <c r="AD5">
         <f>AD3/((1+'Cost Components'!$B$46)^'MFSP Baseline'!AD2)+AD4</f>
-        <v>1128222869.6574645</v>
+        <v>1158059810.9615979</v>
       </c>
       <c r="AE5">
         <f>AE3/((1+'Cost Components'!$B$46)^'MFSP Baseline'!AE2)+AE4</f>
-        <v>1087311224.9636617</v>
+        <v>1115196216.8366833</v>
       </c>
       <c r="AF5">
         <f>AF3/((1+'Cost Components'!$B$46)^'MFSP Baseline'!AF2)+AF4</f>
-        <v>1049076043.0068364</v>
+        <v>1075136783.0750811</v>
       </c>
     </row>
     <row r="6" spans="1:32">
@@ -22049,7 +22049,7 @@
       </c>
       <c r="B9">
         <f>SUM(B5:AF5) / SUM(B7:AF7)</f>
-        <v>6.7170632102834826</v>
+        <v>6.965039460283486</v>
       </c>
     </row>
     <row r="11" spans="1:32">
@@ -22164,123 +22164,123 @@
       </c>
       <c r="C13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="D13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="E13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="F13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="G13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="H13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="I13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="J13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="K13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="L13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="M13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="N13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="O13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="P13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="Q13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="R13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="S13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="T13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="U13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="V13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="W13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="X13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="Y13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="Z13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="AA13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="AB13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="AC13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="AD13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="AE13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
       <c r="AF13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1346568210.6372774</v>
+        <v>1442415210.6372774</v>
       </c>
     </row>
     <row r="14" spans="1:32">
@@ -22420,123 +22420,123 @@
       </c>
       <c r="C15">
         <f>C13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!C12) + C14</f>
-        <v>1559545766.7299201</v>
+        <v>1649122402.2439387</v>
       </c>
       <c r="D15">
         <f>D13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!D12) + D14</f>
-        <v>1477215628.9496691</v>
+        <v>1560932110.7384715</v>
       </c>
       <c r="E15">
         <f>E13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!E12) + E14</f>
-        <v>1400271574.9494343</v>
+        <v>1478511277.5557919</v>
       </c>
       <c r="F15">
         <f>F13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!F12) + F14</f>
-        <v>1328361244.1080937</v>
+        <v>1401482461.4972129</v>
       </c>
       <c r="G15">
         <f>G13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!G12) + G14</f>
-        <v>1261155327.4339435</v>
+        <v>1329492913.7789145</v>
       </c>
       <c r="H15">
         <f>H13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!H12) + H14</f>
-        <v>1198346059.5141768</v>
+        <v>1262212962.6403182</v>
       </c>
       <c r="I15">
         <f>I13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!I12) + I14</f>
-        <v>1139645809.1218717</v>
+        <v>1199334503.6322839</v>
       </c>
       <c r="J15">
         <f>J13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!J12) + J14</f>
-        <v>1084785762.0262592</v>
+        <v>1140569588.6715045</v>
       </c>
       <c r="K15">
         <f>K13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!K12) + K14</f>
-        <v>1033514689.9742851</v>
+        <v>1085649107.3997478</v>
       </c>
       <c r="L15">
         <f>L13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!L12) + L14</f>
-        <v>985597800.20608497</v>
+        <v>1034321554.8093212</v>
       </c>
       <c r="M15">
         <f>M13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!M12) + M14</f>
-        <v>940815660.23580432</v>
+        <v>986351879.4911654</v>
       </c>
       <c r="N15">
         <f>N13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!N12) + N14</f>
-        <v>898963192.97386003</v>
+        <v>941520407.23120689</v>
       </c>
       <c r="O15">
         <f>O13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!O12) + O14</f>
-        <v>859848737.58886528</v>
+        <v>899621835.02563787</v>
       </c>
       <c r="P15">
         <f>P13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!P12) + P14</f>
-        <v>823293171.80849636</v>
+        <v>860464290.90828395</v>
       </c>
       <c r="Q15">
         <f>Q13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!Q12) + Q14</f>
-        <v>789129091.63992715</v>
+        <v>823868455.28458834</v>
       </c>
       <c r="R15">
         <f>R13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!R12) + R14</f>
-        <v>757200044.75341403</v>
+        <v>789666739.74842453</v>
       </c>
       <c r="S15">
         <f>S13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!S12) + S14</f>
-        <v>727359814.01835501</v>
+        <v>757702519.62116861</v>
       </c>
       <c r="T15">
         <f>T13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!T12) + T14</f>
-        <v>699471747.91082311</v>
+        <v>727829416.69849944</v>
       </c>
       <c r="U15">
         <f>U13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!U12) + U14</f>
-        <v>673408134.72621393</v>
+        <v>699910628.92030382</v>
       </c>
       <c r="V15">
         <f>V13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!V12) + V14</f>
-        <v>649049617.73125219</v>
+        <v>673818303.89395308</v>
       </c>
       <c r="W15">
         <f>W13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!W12) + W14</f>
-        <v>626284648.57708216</v>
+        <v>649432953.40203619</v>
       </c>
       <c r="X15">
         <f>X13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!X12) + X14</f>
-        <v>605008976.47038126</v>
+        <v>626642906.21332908</v>
       </c>
       <c r="Y15">
         <f>Y13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!Y12) + Y14</f>
-        <v>585125170.76318419</v>
+        <v>605343796.69117272</v>
       </c>
       <c r="Z15">
         <f>Z13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!Z12) + Z14</f>
-        <v>566542174.77514958</v>
+        <v>585438086.85738182</v>
       </c>
       <c r="AA15">
         <f>AA13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!AA12) + AA14</f>
-        <v>549174888.80502367</v>
+        <v>566834619.72299767</v>
       </c>
       <c r="AB15">
         <f>AB13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!AB12) + AB14</f>
-        <v>532943780.42172849</v>
+        <v>549448201.84039581</v>
       </c>
       <c r="AC15">
         <f>AC13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!AC12) + AC14</f>
-        <v>517774520.2504245</v>
+        <v>533199213.16506696</v>
       </c>
       <c r="AD15">
         <f>AD13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!AD12) + AD14</f>
-        <v>503597641.5856545</v>
+        <v>518013242.44046056</v>
       </c>
       <c r="AE15">
         <f>AE13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!AE12) + AE14</f>
-        <v>490348222.27278531</v>
+        <v>503820746.43615544</v>
       </c>
       <c r="AF15">
         <f>AF13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!AF12) + AF14</f>
-        <v>477965587.40094501</v>
+        <v>490556731.47886097</v>
       </c>
     </row>
     <row r="16" spans="1:32">
@@ -22801,7 +22801,7 @@
       </c>
       <c r="B19">
         <f>SUM(B15:AF15) / SUM(B17:AF17)</f>
-        <v>2.5930432604594715</v>
+        <v>2.7128520104594722</v>
       </c>
     </row>
     <row r="21" spans="1:32" s="24" customFormat="1"/>
@@ -22917,123 +22917,123 @@
       </c>
       <c r="C25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="D25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="E25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="F25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="G25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="H25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="I25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="J25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="K25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="L25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="M25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="N25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="O25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="P25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="Q25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="R25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="S25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="T25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="U25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="V25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="W25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="X25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="Y25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="Z25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="AA25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="AB25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="AC25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="AD25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="AE25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
       <c r="AF25">
         <f xml:space="preserve"> 'Cost Components'!$H$45 * 10^6</f>
-        <v>4150052237.9706106</v>
+        <v>4348433237.9706106</v>
       </c>
     </row>
     <row r="26" spans="1:32">
@@ -23174,123 +23174,123 @@
       </c>
       <c r="C27">
         <f>C25/((1+'Cost Components'!$H$46)^'MFSP Baseline'!C24) + C26</f>
-        <v>4277939709.2315445</v>
+        <v>4463342512.969862</v>
       </c>
       <c r="D27">
         <f>D25/((1+'Cost Components'!$H$46)^'MFSP Baseline'!D24) + D26</f>
-        <v>4024202564.8015127</v>
+        <v>4197476213.1550808</v>
       </c>
       <c r="E27">
         <f>E25/((1+'Cost Components'!$H$46)^'MFSP Baseline'!E24) + E26</f>
-        <v>3787065046.6426048</v>
+        <v>3949003035.7580891</v>
       </c>
       <c r="F27">
         <f>F25/((1+'Cost Components'!$H$46)^'MFSP Baseline'!F24) + F26</f>
-        <v>3565441197.8959627</v>
+        <v>3716785112.9571629</v>
       </c>
       <c r="G27">
         <f>G25/((1+'Cost Components'!$H$46)^'MFSP Baseline'!G24) + G26</f>
-        <v>3358316105.6093807</v>
+        <v>3499759016.8815298</v>
       </c>
       <c r="H27">
         <f>H25/((1+'Cost Components'!$H$46)^'MFSP Baseline'!H24) + H26</f>
-        <v>3164741253.0050983</v>
+        <v>3296930889.7080421</v>
       </c>
       <c r="I27">
         <f>I25/((1+'Cost Components'!$H$46)^'MFSP Baseline'!I24) + I26</f>
-        <v>2983830175.8048344</v>
+        <v>3107371892.3496418</v>
       </c>
       <c r="J27">
         <f>J25/((1+'Cost Components'!$H$46)^'MFSP Baseline'!J24) + J26</f>
-        <v>2814754402.7204762</v>
+        <v>2930213950.8931932</v>
       </c>
       <c r="K27">
         <f>K25/((1+'Cost Components'!$H$46)^'MFSP Baseline'!K24) + K26</f>
-        <v>2656739661.5201406</v>
+        <v>2764645781.3077269</v>
       </c>
       <c r="L27">
         <f>L25/((1+'Cost Components'!$H$46)^'MFSP Baseline'!L24) + L26</f>
-        <v>2509062333.2955284</v>
+        <v>2609909174.2185059</v>
       </c>
       <c r="M27">
         <f>M25/((1+'Cost Components'!$H$46)^'MFSP Baseline'!M24) + M26</f>
-        <v>2371046138.6930866</v>
+        <v>2465295522.7332525</v>
       </c>
       <c r="N27">
         <f>N25/((1+'Cost Components'!$H$46)^'MFSP Baseline'!N24) + N26</f>
-        <v>2242059040.9337959</v>
+        <v>2330142577.4199324</v>
       </c>
       <c r="O27">
         <f>O25/((1+'Cost Components'!$H$46)^'MFSP Baseline'!O24) + O26</f>
-        <v>2121510351.4391315</v>
+        <v>2203831413.5757074</v>
       </c>
       <c r="P27">
         <f>P25/((1+'Cost Components'!$H$46)^'MFSP Baseline'!P24) + P26</f>
-        <v>2008848024.808604</v>
+        <v>2085783596.8988619</v>
       </c>
       <c r="Q27">
         <f>Q25/((1+'Cost Components'!$H$46)^'MFSP Baseline'!Q24) + Q26</f>
-        <v>1903556130.7613819</v>
+        <v>1975458534.5840528</v>
       </c>
       <c r="R27">
         <f>R25/((1+'Cost Components'!$H$46)^'MFSP Baseline'!R24) + R26</f>
-        <v>1805152491.4649127</v>
+        <v>1872350999.7103996</v>
       </c>
       <c r="S27">
         <f>S25/((1+'Cost Components'!$H$46)^'MFSP Baseline'!S24) + S26</f>
-        <v>1713186473.4308293</v>
+        <v>1775988817.58549</v>
       </c>
       <c r="T27">
         <f>T25/((1+'Cost Components'!$H$46)^'MFSP Baseline'!T24) + T26</f>
-        <v>1627236923.8662655</v>
+        <v>1685930703.4500604</v>
       </c>
       <c r="U27">
         <f>U25/((1+'Cost Components'!$H$46)^'MFSP Baseline'!U24) + U26</f>
-        <v>1546910242.0302243</v>
+        <v>1601764241.6412477</v>
       </c>
       <c r="V27">
         <f>V25/((1+'Cost Components'!$H$46)^'MFSP Baseline'!V24) + V26</f>
-        <v>1471838576.7628965</v>
+        <v>1523103996.9601145</v>
       </c>
       <c r="W27">
         <f>W25/((1+'Cost Components'!$H$46)^'MFSP Baseline'!W24) + W26</f>
-        <v>1401678141.9336178</v>
+        <v>1449589749.5945692</v>
       </c>
       <c r="X27">
         <f>X25/((1+'Cost Components'!$H$46)^'MFSP Baseline'!X24) + X26</f>
-        <v>1336107642.0931706</v>
+        <v>1380884845.5146205</v>
       </c>
       <c r="Y27">
         <f>Y25/((1+'Cost Components'!$H$46)^'MFSP Baseline'!Y24) + Y26</f>
-        <v>1274826801.12079</v>
+        <v>1316674654.7856965</v>
       </c>
       <c r="Z27">
         <f>Z25/((1+'Cost Components'!$H$46)^'MFSP Baseline'!Z24) + Z26</f>
-        <v>1217554987.1279109</v>
+        <v>1256665130.7399731</v>
       </c>
       <c r="AA27">
         <f>AA25/((1+'Cost Components'!$H$46)^'MFSP Baseline'!AA24) + AA26</f>
-        <v>1164029927.3214817</v>
+        <v>1200581463.4075212</v>
       </c>
       <c r="AB27">
         <f>AB25/((1+'Cost Components'!$H$46)^'MFSP Baseline'!AB24) + AB26</f>
-        <v>1114006506.9416418</v>
+        <v>1148166821.0407438</v>
       </c>
       <c r="AC27">
         <f>AC25/((1+'Cost Components'!$H$46)^'MFSP Baseline'!AC24) + AC26</f>
-        <v>1067255646.7735665</v>
+        <v>1099181173.9689894</v>
       </c>
       <c r="AD27">
         <f>AD25/((1+'Cost Components'!$H$46)^'MFSP Baseline'!AD24) + AD26</f>
-        <v>1023563254.0931227</v>
+        <v>1053400195.3972561</v>
       </c>
       <c r="AE27">
         <f>AE25/((1+'Cost Components'!$H$46)^'MFSP Baseline'!AE24) + AE26</f>
-        <v>982729242.24224067</v>
+        <v>1010614234.1152624</v>
       </c>
       <c r="AF27">
         <f>AF25/((1+'Cost Components'!$H$46)^'MFSP Baseline'!AF24) + AF26</f>
-        <v>944566614.34421992</v>
+        <v>970627354.41246462</v>
       </c>
     </row>
     <row r="28" spans="1:32">
@@ -23556,7 +23556,7 @@
       </c>
       <c r="B31">
         <f>SUM(B27:AF27) / SUM(B29:AF29)</f>
-        <v>6.3945065003377843</v>
+        <v>6.6424827503377841</v>
       </c>
     </row>
     <row r="33" spans="1:32">
@@ -23671,123 +23671,123 @@
       </c>
       <c r="C36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="D36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="E36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="F36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="G36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="H36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="I36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="J36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="K36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="L36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="M36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="N36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="O36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="P36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="Q36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="R36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="S36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="T36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="U36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="V36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="W36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="X36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="Y36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="Z36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="AA36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="AB36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="AC36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="AD36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="AE36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
       <c r="AF36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1349798210.6372774</v>
+        <v>1445645210.6372774</v>
       </c>
     </row>
     <row r="37" spans="1:32">
@@ -23928,123 +23928,123 @@
       </c>
       <c r="C38">
         <f>C36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!C35) + C37</f>
-        <v>1565304396.0380828</v>
+        <v>1654881031.5521016</v>
       </c>
       <c r="D38">
         <f>D36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!D35) + D37</f>
-        <v>1482776773.7613692</v>
+        <v>1566493255.5501719</v>
       </c>
       <c r="E38">
         <f>E36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!E35) + E37</f>
-        <v>1405648154.8111696</v>
+        <v>1483887857.417527</v>
       </c>
       <c r="F38">
         <f>F36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!F35) + F37</f>
-        <v>1333565333.362385</v>
+        <v>1406686550.7515042</v>
       </c>
       <c r="G38">
         <f>G36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!G35) + G37</f>
-        <v>1266198210.5130534</v>
+        <v>1334535796.8580246</v>
       </c>
       <c r="H38">
         <f>H36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!H35) + H37</f>
-        <v>1203238282.616482</v>
+        <v>1267105185.7426233</v>
       </c>
       <c r="I38">
         <f>I36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!I35) + I37</f>
-        <v>1144397228.5075366</v>
+        <v>1204085923.0179491</v>
       </c>
       <c r="J38">
         <f>J36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!J35) + J37</f>
-        <v>1089405589.1533821</v>
+        <v>1145189415.7986274</v>
       </c>
       <c r="K38">
         <f>K36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!K35) + K37</f>
-        <v>1038011533.6822095</v>
+        <v>1090145951.1076725</v>
       </c>
       <c r="L38">
         <f>L36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!L35) + L37</f>
-        <v>989979706.13905787</v>
+        <v>1038703460.7422941</v>
       </c>
       <c r="M38">
         <f>M36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!M35) + M37</f>
-        <v>945090147.68751407</v>
+        <v>990626366.94287515</v>
       </c>
       <c r="N38">
         <f>N36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!N35) + N37</f>
-        <v>903137289.32158542</v>
+        <v>945694503.57893205</v>
       </c>
       <c r="O38">
         <f>O36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!O35) + O37</f>
-        <v>863929010.4749229</v>
+        <v>903702107.91169572</v>
       </c>
       <c r="P38">
         <f>P36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!P35) + P37</f>
-        <v>827285759.21636009</v>
+        <v>864456878.31614757</v>
       </c>
       <c r="Q38">
         <f>Q36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!Q35) + Q37</f>
-        <v>793039730.00274968</v>
+        <v>827779093.64741099</v>
       </c>
       <c r="R38">
         <f>R36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!R35) + R37</f>
-        <v>761034095.22367477</v>
+        <v>793500790.21868539</v>
       </c>
       <c r="S38">
         <f>S36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!S35) + S37</f>
-        <v>731122287.01893187</v>
+        <v>761464992.62174535</v>
       </c>
       <c r="T38">
         <f>T36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!T35) + T37</f>
-        <v>703167326.0799197</v>
+        <v>731524994.86759591</v>
       </c>
       <c r="U38">
         <f>U36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!U35) + U37</f>
-        <v>677041194.36121678</v>
+        <v>703543688.55530667</v>
       </c>
       <c r="V38">
         <f>V36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!V35) + V37</f>
-        <v>652624248.82971871</v>
+        <v>677392934.9924196</v>
       </c>
       <c r="W38">
         <f>W36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!W35) + W37</f>
-        <v>629804673.56663632</v>
+        <v>652952978.39159048</v>
       </c>
       <c r="X38">
         <f>X36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!X35) + X37</f>
-        <v>608477967.71328843</v>
+        <v>630111897.45623612</v>
       </c>
       <c r="Y38">
         <f>Y36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!Y35) + Y37</f>
-        <v>588546466.91576695</v>
+        <v>608765092.84375548</v>
       </c>
       <c r="Z38">
         <f>Z36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!Z35) + Z37</f>
-        <v>569918896.07696187</v>
+        <v>588814808.15919423</v>
       </c>
       <c r="AA38">
         <f>AA36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!AA35) + AA37</f>
-        <v>552509951.36779821</v>
+        <v>570169682.28577232</v>
       </c>
       <c r="AB38">
         <f>AB36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!AB35) + AB37</f>
-        <v>536239909.58353317</v>
+        <v>552744331.0022006</v>
       </c>
       <c r="AC38">
         <f>AC36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!AC35) + AC37</f>
-        <v>521034263.05618262</v>
+        <v>536458955.97082496</v>
       </c>
       <c r="AD38">
         <f>AD36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!AD35) + AD37</f>
-        <v>506823378.45118213</v>
+        <v>521238979.30598807</v>
       </c>
       <c r="AE38">
         <f>AE36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!AE35) + AE37</f>
-        <v>493542177.88576108</v>
+        <v>507014702.04913116</v>
       </c>
       <c r="AF38">
         <f>AF36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!AF35) + AF37</f>
-        <v>481129840.90873206</v>
+        <v>493720984.98664808</v>
       </c>
     </row>
     <row r="39" spans="1:32">
@@ -24310,7 +24310,7 @@
       </c>
       <c r="B42">
         <f>SUM(B38:AF38) / SUM(B40:AF40)</f>
-        <v>2.6053608252088116</v>
+        <v>2.7251695752088123</v>
       </c>
     </row>
     <row r="44" spans="1:32" s="24" customFormat="1"/>
@@ -24426,123 +24426,123 @@
       </c>
       <c r="C49">
         <f xml:space="preserve"> 'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="D49">
         <f xml:space="preserve"> 'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="E49">
         <f xml:space="preserve"> 'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="F49">
         <f xml:space="preserve"> 'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="G49">
         <f xml:space="preserve"> 'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="H49">
         <f xml:space="preserve"> 'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="I49">
         <f xml:space="preserve"> 'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="J49">
         <f xml:space="preserve"> 'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="K49">
         <f xml:space="preserve"> 'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="L49">
         <f xml:space="preserve"> 'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="M49">
         <f xml:space="preserve"> 'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="N49">
         <f xml:space="preserve"> 'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="O49">
         <f xml:space="preserve"> 'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="P49">
         <f xml:space="preserve"> 'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="Q49">
         <f xml:space="preserve"> 'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="R49">
         <f xml:space="preserve"> 'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="S49">
         <f xml:space="preserve"> 'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="T49">
         <f xml:space="preserve"> 'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="U49">
         <f xml:space="preserve"> 'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="V49">
         <f xml:space="preserve"> 'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="W49">
         <f xml:space="preserve"> 'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="X49">
         <f xml:space="preserve"> 'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="Y49">
         <f xml:space="preserve"> 'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="Z49">
         <f xml:space="preserve"> 'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="AA49">
         <f xml:space="preserve"> 'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="AB49">
         <f xml:space="preserve"> 'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="AC49">
         <f xml:space="preserve"> 'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="AD49">
         <f xml:space="preserve"> 'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="AE49">
         <f xml:space="preserve"> 'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
       <c r="AF49">
         <f xml:space="preserve"> 'Cost Components'!$N$45 * 10^6</f>
-        <v>4163862237.9706101</v>
+        <v>4362243237.9706106</v>
       </c>
     </row>
     <row r="50" spans="1:32">
@@ -24682,123 +24682,123 @@
       </c>
       <c r="C51">
         <f>C49/((1+'Cost Components'!$N$46)^'MFSP Baseline'!C48) + C50</f>
-        <v>4407535363.5717077</v>
+        <v>4592938167.3100262</v>
       </c>
       <c r="D51">
         <f>D49/((1+'Cost Components'!$N$46)^'MFSP Baseline'!D48) + D50</f>
-        <v>4152953865.9230547</v>
+        <v>4326227514.2766228</v>
       </c>
       <c r="E51">
         <f>E49/((1+'Cost Components'!$N$46)^'MFSP Baseline'!E48) + E50</f>
-        <v>3915027232.6065564</v>
+        <v>4076965221.7220407</v>
       </c>
       <c r="F51">
         <f>F49/((1+'Cost Components'!$N$46)^'MFSP Baseline'!F48) + F50</f>
-        <v>3692665893.0584273</v>
+        <v>3844009808.119628</v>
       </c>
       <c r="G51">
         <f>G49/((1+'Cost Components'!$N$46)^'MFSP Baseline'!G48) + G50</f>
-        <v>3484851557.0321383</v>
+        <v>3626294468.3042884</v>
       </c>
       <c r="H51">
         <f>H49/((1+'Cost Components'!$N$46)^'MFSP Baseline'!H48) + H50</f>
-        <v>3290632551.4000931</v>
+        <v>3422822188.1030369</v>
       </c>
       <c r="I51">
         <f>I49/((1+'Cost Components'!$N$46)^'MFSP Baseline'!I48) + I50</f>
-        <v>3109119462.0243492</v>
+        <v>3232661178.5691566</v>
       </c>
       <c r="J51">
         <f>J49/((1+'Cost Components'!$N$46)^'MFSP Baseline'!J48) + J50</f>
-        <v>2939481060.7386079</v>
+        <v>3054940608.911325</v>
       </c>
       <c r="K51">
         <f>K49/((1+'Cost Components'!$N$46)^'MFSP Baseline'!K48) + K50</f>
-        <v>2780940498.7893162</v>
+        <v>2888846618.5769024</v>
       </c>
       <c r="L51">
         <f>L49/((1+'Cost Components'!$N$46)^'MFSP Baseline'!L48) + L50</f>
-        <v>2632771749.3039975</v>
+        <v>2733618590.226975</v>
       </c>
       <c r="M51">
         <f>M49/((1+'Cost Components'!$N$46)^'MFSP Baseline'!M48) + M50</f>
-        <v>2494296282.4952879</v>
+        <v>2588545666.5354543</v>
       </c>
       <c r="N51">
         <f>N49/((1+'Cost Components'!$N$46)^'MFSP Baseline'!N48) + N50</f>
-        <v>2364879958.3749995</v>
+        <v>2452963494.861136</v>
       </c>
       <c r="O51">
         <f>O49/((1+'Cost Components'!$N$46)^'MFSP Baseline'!O48) + O50</f>
-        <v>2243930122.7485609</v>
+        <v>2326251184.8851371</v>
       </c>
       <c r="P51">
         <f>P49/((1+'Cost Components'!$N$46)^'MFSP Baseline'!P48) + P50</f>
-        <v>2130892893.1911421</v>
+        <v>2207828465.2814002</v>
       </c>
       <c r="Q51">
         <f>Q49/((1+'Cost Components'!$N$46)^'MFSP Baseline'!Q48) + Q50</f>
-        <v>2025250622.5767317</v>
+        <v>2097153026.3994029</v>
       </c>
       <c r="R51">
         <f>R49/((1+'Cost Components'!$N$46)^'MFSP Baseline'!R48) + R50</f>
-        <v>1926519528.5445728</v>
+        <v>1993718036.7900598</v>
       </c>
       <c r="S51">
         <f>S49/((1+'Cost Components'!$N$46)^'MFSP Baseline'!S48) + S50</f>
-        <v>1834247478.0472276</v>
+        <v>1897049822.2018886</v>
       </c>
       <c r="T51">
         <f>T49/((1+'Cost Components'!$N$46)^'MFSP Baseline'!T48) + T50</f>
-        <v>1748011916.8347557</v>
+        <v>1806705696.4185507</v>
       </c>
       <c r="U51">
         <f>U49/((1+'Cost Components'!$N$46)^'MFSP Baseline'!U48) + U50</f>
-        <v>1667417934.393193</v>
+        <v>1722271934.0042164</v>
       </c>
       <c r="V51">
         <f>V49/((1+'Cost Components'!$N$46)^'MFSP Baseline'!V48) + V50</f>
-        <v>1592096455.4758449</v>
+        <v>1643361875.673063</v>
       </c>
       <c r="W51">
         <f>W49/((1+'Cost Components'!$N$46)^'MFSP Baseline'!W48) + W50</f>
-        <v>1521702549.9456129</v>
+        <v>1569614157.6065645</v>
       </c>
       <c r="X51">
         <f>X49/((1+'Cost Components'!$N$46)^'MFSP Baseline'!X48) + X50</f>
-        <v>1455913853.1883867</v>
+        <v>1500691056.6098368</v>
       </c>
       <c r="Y51">
         <f>Y49/((1+'Cost Components'!$N$46)^'MFSP Baseline'!Y48) + Y50</f>
-        <v>1394429089.8638763</v>
+        <v>1436276943.5287828</v>
       </c>
       <c r="Z51">
         <f>Z49/((1+'Cost Components'!$N$46)^'MFSP Baseline'!Z48) + Z50</f>
-        <v>1336966694.2334926</v>
+        <v>1376076837.8455551</v>
       </c>
       <c r="AA51">
         <f>AA49/((1+'Cost Components'!$N$46)^'MFSP Baseline'!AA48) + AA50</f>
-        <v>1283263520.7471528</v>
+        <v>1319815056.8331923</v>
       </c>
       <c r="AB51">
         <f>AB49/((1+'Cost Components'!$N$46)^'MFSP Baseline'!AB48) + AB50</f>
-        <v>1233073638.9842186</v>
+        <v>1267233953.0833209</v>
       </c>
       <c r="AC51">
         <f>AC49/((1+'Cost Components'!$N$46)^'MFSP Baseline'!AC48) + AC50</f>
-        <v>1186167207.4300742</v>
+        <v>1218092734.6254969</v>
       </c>
       <c r="AD51">
         <f>AD49/((1+'Cost Components'!$N$46)^'MFSP Baseline'!AD48) + AD50</f>
-        <v>1142329420.9308741</v>
+        <v>1172166362.2350075</v>
       </c>
       <c r="AE51">
         <f>AE49/((1+'Cost Components'!$N$46)^'MFSP Baseline'!AE48) + AE50</f>
-        <v>1101359527.0063877</v>
+        <v>1129244518.8794098</v>
       </c>
       <c r="AF51">
         <f>AF49/((1+'Cost Components'!$N$46)^'MFSP Baseline'!AF48) + AF50</f>
-        <v>1063069906.5162139</v>
+        <v>1089130646.5844586</v>
       </c>
     </row>
     <row r="52" spans="1:32">
@@ -25063,7 +25063,7 @@
       </c>
       <c r="B55">
         <f>SUM(B51:AF51) / SUM(B53:AF53)</f>
-        <v>6.7644023461332434</v>
+        <v>7.0123785961332468</v>
       </c>
     </row>
     <row r="57" spans="1:32">
@@ -25178,123 +25178,123 @@
       </c>
       <c r="C59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="D59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="E59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="F59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="G59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="H59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="I59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="J59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="K59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="L59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="M59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="N59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="O59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="P59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="Q59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="R59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="S59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="T59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="U59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="V59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="W59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="X59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="Y59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="Z59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="AA59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="AB59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="AC59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="AD59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="AE59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
       <c r="AF59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1347568210.6372774</v>
+        <v>1443415210.6372774</v>
       </c>
     </row>
     <row r="60" spans="1:32">
@@ -25434,123 +25434,123 @@
       </c>
       <c r="C61">
         <f>C59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!C58) + C60</f>
-        <v>1559755068.5375724</v>
+        <v>1649331704.0515912</v>
       </c>
       <c r="D61">
         <f>D59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!D58) + D60</f>
-        <v>1477363790.0463424</v>
+        <v>1561080271.8351448</v>
       </c>
       <c r="E61">
         <f>E59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!E58) + E60</f>
-        <v>1400362595.1947253</v>
+        <v>1478602297.8010828</v>
       </c>
       <c r="F61">
         <f>F59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!F58) + F60</f>
-        <v>1328398861.6885414</v>
+        <v>1401520079.0776606</v>
       </c>
       <c r="G61">
         <f>G59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!G58) + G60</f>
-        <v>1261143035.9818273</v>
+        <v>1329480622.3267984</v>
       </c>
       <c r="H61">
         <f>H59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!H58) + H60</f>
-        <v>1198287124.1063933</v>
+        <v>1262154027.2325349</v>
       </c>
       <c r="I61">
         <f>I59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!I58) + I60</f>
-        <v>1139543281.2321563</v>
+        <v>1199231975.7425685</v>
       </c>
       <c r="J61">
         <f>J59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!J58) + J60</f>
-        <v>1084642493.4992244</v>
+        <v>1140426320.1444697</v>
       </c>
       <c r="K61">
         <f>K59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!K58) + K60</f>
-        <v>1033333346.0852692</v>
+        <v>1085467763.5107322</v>
       </c>
       <c r="L61">
         <f>L59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!L58) + L60</f>
-        <v>985380871.86661971</v>
+        <v>1034104626.469856</v>
       </c>
       <c r="M61">
         <f>M59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!M58) + M60</f>
-        <v>940565475.40059197</v>
+        <v>986101694.65595305</v>
       </c>
       <c r="N61">
         <f>N59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!N58) + N60</f>
-        <v>898681927.3015008</v>
+        <v>941239141.55884755</v>
       </c>
       <c r="O61">
         <f>O59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!O58) + O60</f>
-        <v>859538424.40515387</v>
+        <v>899311521.84192646</v>
       </c>
       <c r="P61">
         <f>P59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!P58) + P60</f>
-        <v>822955711.41791368</v>
+        <v>860126830.51770127</v>
       </c>
       <c r="Q61">
         <f>Q59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!Q58) + Q60</f>
-        <v>788766260.0279696</v>
+        <v>823505623.67263079</v>
       </c>
       <c r="R61">
         <f>R59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!R58) + R60</f>
-        <v>756813501.71961069</v>
+        <v>789280196.71462119</v>
       </c>
       <c r="S61">
         <f>S59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!S58) + S60</f>
-        <v>726951110.77721918</v>
+        <v>757293816.38003278</v>
       </c>
       <c r="T61">
         <f>T59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!T58) + T60</f>
-        <v>699042334.19554472</v>
+        <v>727400002.98322105</v>
       </c>
       <c r="U61">
         <f>U59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!U58) + U60</f>
-        <v>672959365.42762482</v>
+        <v>699461859.62171483</v>
       </c>
       <c r="V61">
         <f>V59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!V58) + V60</f>
-        <v>648582759.10246611</v>
+        <v>673351445.265167</v>
       </c>
       <c r="W61">
         <f>W59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!W58) + W60</f>
-        <v>625800884.03222418</v>
+        <v>648949188.85717821</v>
       </c>
       <c r="X61">
         <f>X59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!X58) + X60</f>
-        <v>604509412.00396073</v>
+        <v>626143341.74690843</v>
       </c>
       <c r="Y61">
         <f>Y59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!Y58) + Y60</f>
-        <v>584610840.01492941</v>
+        <v>604829465.94291806</v>
       </c>
       <c r="Z61">
         <f>Z59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!Z58) + Z60</f>
-        <v>566014043.76349831</v>
+        <v>584909955.84573054</v>
       </c>
       <c r="AA61">
         <f>AA59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!AA58) + AA60</f>
-        <v>548633860.35094595</v>
+        <v>566293591.26891994</v>
       </c>
       <c r="AB61">
         <f>AB59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!AB58) + AB60</f>
-        <v>532390698.28313994</v>
+        <v>548895119.70180726</v>
       </c>
       <c r="AC61">
         <f>AC59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!AC58) + AC60</f>
-        <v>517210172.98612499</v>
+        <v>532634865.90076733</v>
       </c>
       <c r="AD61">
         <f>AD59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!AD58) + AD60</f>
-        <v>503022766.16648483</v>
+        <v>517438367.02129084</v>
       </c>
       <c r="AE61">
         <f>AE59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!AE58) + AE60</f>
-        <v>489763507.45654082</v>
+        <v>503236031.6199109</v>
       </c>
       <c r="AF61">
         <f>AF59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!AF58) + AF60</f>
-        <v>477371676.88649964</v>
+        <v>489962820.96441561</v>
       </c>
     </row>
     <row r="62" spans="1:32">
@@ -25815,7 +25815,7 @@
       </c>
       <c r="B65">
         <f>SUM(B61:AF61) / SUM(B63:AF63)</f>
-        <v>2.5921014786140577</v>
+        <v>2.7119102286140579</v>
       </c>
     </row>
     <row r="71" spans="1:32">
@@ -25977,123 +25977,123 @@
       </c>
       <c r="C3">
         <f>('Cost Components'!$B$44 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!C1</f>
-        <v>2670633644.8598123</v>
+        <v>2856036448.5981302</v>
       </c>
       <c r="D3">
         <f>('Cost Components'!$B$44 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!D1</f>
-        <v>2495919294.261507</v>
+        <v>2669192942.6150751</v>
       </c>
       <c r="E3">
         <f>('Cost Components'!$B$44 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!E1</f>
-        <v>2332634854.4500065</v>
+        <v>2494572843.5654907</v>
       </c>
       <c r="F3">
         <f>('Cost Components'!$B$44 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!F1</f>
-        <v>2180032574.2523427</v>
+        <v>2331376489.3135428</v>
       </c>
       <c r="G3">
         <f>('Cost Components'!$B$44 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!G1</f>
-        <v>2037413620.7965817</v>
+        <v>2178856532.0687313</v>
       </c>
       <c r="H3">
         <f>('Cost Components'!$B$44 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!H1</f>
-        <v>1904124879.2491419</v>
+        <v>2036314515.9520855</v>
       </c>
       <c r="I3">
         <f>('Cost Components'!$B$44 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!I1</f>
-        <v>1779555961.9150858</v>
+        <v>1903097678.4598927</v>
       </c>
       <c r="J3">
         <f>('Cost Components'!$B$44 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!J1</f>
-        <v>1663136413.0047531</v>
+        <v>1778595961.17747</v>
       </c>
       <c r="K3">
         <f>('Cost Components'!$B$44 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!K1</f>
-        <v>1554333096.2661242</v>
+        <v>1662239216.0537102</v>
       </c>
       <c r="L3">
         <f>('Cost Components'!$B$44 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!L1</f>
-        <v>1452647753.5197425</v>
+        <v>1553494594.4427199</v>
       </c>
       <c r="M3">
         <f>('Cost Components'!$B$44 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!M1</f>
-        <v>1357614722.9156468</v>
+        <v>1451864106.9558127</v>
       </c>
       <c r="N3">
         <f>('Cost Components'!$B$44 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!N1</f>
-        <v>1268798806.4632215</v>
+        <v>1356882342.949358</v>
       </c>
       <c r="O3">
         <f>('Cost Components'!$B$44 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!O1</f>
-        <v>1185793277.0684314</v>
+        <v>1268114339.2050073</v>
       </c>
       <c r="P3">
         <f>('Cost Components'!$B$44 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!P1</f>
-        <v>1108218015.9518051</v>
+        <v>1185153588.042063</v>
       </c>
       <c r="Q3">
         <f>('Cost Components'!$B$44 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!Q1</f>
-        <v>1035717771.9175746</v>
+        <v>1107620175.7402456</v>
       </c>
       <c r="R3">
         <f>('Cost Components'!$B$44 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!R1</f>
-        <v>967960534.50240636</v>
+        <v>1035159042.7478932</v>
       </c>
       <c r="S3">
         <f>('Cost Components'!$B$44 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!S1</f>
-        <v>904636013.55365086</v>
+        <v>967438357.70831144</v>
       </c>
       <c r="T3">
         <f>('Cost Components'!$B$44 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!T1</f>
-        <v>845454218.27444005</v>
+        <v>904147997.858235</v>
       </c>
       <c r="U3">
         <f>('Cost Components'!$B$44 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!U1</f>
-        <v>790144129.22844851</v>
+        <v>844998128.83947194</v>
       </c>
       <c r="V3">
         <f>('Cost Components'!$B$44 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!V1</f>
-        <v>738452457.22284913</v>
+        <v>789717877.42006731</v>
       </c>
       <c r="W3">
         <f>('Cost Components'!$B$44 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!W1</f>
-        <v>690142483.3858403</v>
+        <v>738054091.04679179</v>
       </c>
       <c r="X3">
         <f>('Cost Components'!$B$44 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!X1</f>
-        <v>644992975.1269536</v>
+        <v>689770178.5484035</v>
       </c>
       <c r="Y3">
         <f>('Cost Components'!$B$44 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!Y1</f>
-        <v>602797173.01584446</v>
+        <v>644645026.68075097</v>
       </c>
       <c r="Z3">
         <f>('Cost Components'!$B$44 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!Z1</f>
-        <v>563361843.94004154</v>
+        <v>602471987.55210364</v>
       </c>
       <c r="AA3">
         <f>('Cost Components'!$B$44 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!AA1</f>
-        <v>526506396.20564622</v>
+        <v>563057932.2916857</v>
       </c>
       <c r="AB3">
         <f>('Cost Components'!$B$44 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!AB1</f>
-        <v>492062052.5286414</v>
+        <v>526222366.62774366</v>
       </c>
       <c r="AC3">
         <f>('Cost Components'!$B$44 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!AC1</f>
-        <v>459871077.12957132</v>
+        <v>491796604.32499397</v>
       </c>
       <c r="AD3">
         <f>('Cost Components'!$B$44 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!AD1</f>
-        <v>429786053.39212281</v>
+        <v>459622994.6962561</v>
       </c>
       <c r="AE3">
         <f>('Cost Components'!$B$44 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!AE1</f>
-        <v>401669208.77768481</v>
+        <v>429554200.65070665</v>
       </c>
       <c r="AF3">
         <f>('Cost Components'!$B$44 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!AF1</f>
-        <v>375391783.90437835</v>
+        <v>401452523.97262305</v>
       </c>
     </row>
     <row r="4" spans="1:32">
@@ -26492,7 +26492,7 @@
       </c>
       <c r="B9" s="36">
         <f>SUM(B3:AF3) / SUM($B$3:$AF$6)</f>
-        <v>0.50584246583653325</v>
+        <v>0.52260706801444123</v>
       </c>
     </row>
     <row r="10" spans="1:32">
@@ -26501,7 +26501,7 @@
       </c>
       <c r="B10" s="36">
         <f t="shared" ref="B10:B11" si="0">SUM(B4:AF4) / SUM($B$3:$AF$6)</f>
-        <v>0.21688816575410674</v>
+        <v>0.20953009962218225</v>
       </c>
     </row>
     <row r="11" spans="1:32">
@@ -26510,7 +26510,7 @@
       </c>
       <c r="B11" s="36">
         <f t="shared" si="0"/>
-        <v>0.24511639654309289</v>
+        <v>0.23680067009710556</v>
       </c>
     </row>
     <row r="12" spans="1:32">
@@ -26519,7 +26519,7 @@
       </c>
       <c r="B12" s="36">
         <f>SUM(B6:AF6) / SUM($B$3:$AF$6)</f>
-        <v>3.2152971866267976E-2</v>
+        <v>3.106216226627288E-2</v>
       </c>
     </row>
     <row r="14" spans="1:32" s="2" customFormat="1">
@@ -26536,123 +26536,123 @@
       </c>
       <c r="C15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!C13</f>
-        <v>1069919999.9999999</v>
+        <v>1165766999.9999998</v>
       </c>
       <c r="D15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!D13</f>
-        <v>1069919999.9999999</v>
+        <v>1165766999.9999998</v>
       </c>
       <c r="E15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!E13</f>
-        <v>1069919999.9999999</v>
+        <v>1165766999.9999998</v>
       </c>
       <c r="F15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!F13</f>
-        <v>1069919999.9999999</v>
+        <v>1165766999.9999998</v>
       </c>
       <c r="G15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!G13</f>
-        <v>1069919999.9999999</v>
+        <v>1165766999.9999998</v>
       </c>
       <c r="H15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!H13</f>
-        <v>1069919999.9999999</v>
+        <v>1165766999.9999998</v>
       </c>
       <c r="I15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!I13</f>
-        <v>1069919999.9999999</v>
+        <v>1165766999.9999998</v>
       </c>
       <c r="J15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!J13</f>
-        <v>1069919999.9999999</v>
+        <v>1165766999.9999998</v>
       </c>
       <c r="K15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!K13</f>
-        <v>1069919999.9999999</v>
+        <v>1165766999.9999998</v>
       </c>
       <c r="L15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!L13</f>
-        <v>1069919999.9999999</v>
+        <v>1165766999.9999998</v>
       </c>
       <c r="M15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!M13</f>
-        <v>1069919999.9999999</v>
+        <v>1165766999.9999998</v>
       </c>
       <c r="N15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!N13</f>
-        <v>1069919999.9999999</v>
+        <v>1165766999.9999998</v>
       </c>
       <c r="O15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!O13</f>
-        <v>1069919999.9999999</v>
+        <v>1165766999.9999998</v>
       </c>
       <c r="P15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!P13</f>
-        <v>1069919999.9999999</v>
+        <v>1165766999.9999998</v>
       </c>
       <c r="Q15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!Q13</f>
-        <v>1069919999.9999999</v>
+        <v>1165766999.9999998</v>
       </c>
       <c r="R15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!R13</f>
-        <v>1069919999.9999999</v>
+        <v>1165766999.9999998</v>
       </c>
       <c r="S15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!S13</f>
-        <v>1069919999.9999999</v>
+        <v>1165766999.9999998</v>
       </c>
       <c r="T15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!T13</f>
-        <v>1069919999.9999999</v>
+        <v>1165766999.9999998</v>
       </c>
       <c r="U15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!U13</f>
-        <v>1069919999.9999999</v>
+        <v>1165766999.9999998</v>
       </c>
       <c r="V15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!V13</f>
-        <v>1069919999.9999999</v>
+        <v>1165766999.9999998</v>
       </c>
       <c r="W15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!W13</f>
-        <v>1069919999.9999999</v>
+        <v>1165766999.9999998</v>
       </c>
       <c r="X15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!X13</f>
-        <v>1069919999.9999999</v>
+        <v>1165766999.9999998</v>
       </c>
       <c r="Y15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!Y13</f>
-        <v>1069919999.9999999</v>
+        <v>1165766999.9999998</v>
       </c>
       <c r="Z15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!Z13</f>
-        <v>1069919999.9999999</v>
+        <v>1165766999.9999998</v>
       </c>
       <c r="AA15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!AA13</f>
-        <v>1069919999.9999999</v>
+        <v>1165766999.9999998</v>
       </c>
       <c r="AB15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!AB13</f>
-        <v>1069919999.9999999</v>
+        <v>1165766999.9999998</v>
       </c>
       <c r="AC15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!AC13</f>
-        <v>1069919999.9999999</v>
+        <v>1165766999.9999998</v>
       </c>
       <c r="AD15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!AD13</f>
-        <v>1069919999.9999999</v>
+        <v>1165766999.9999998</v>
       </c>
       <c r="AE15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!AE13</f>
-        <v>1069919999.9999999</v>
+        <v>1165766999.9999998</v>
       </c>
       <c r="AF15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!AF13</f>
-        <v>1069919999.9999999</v>
+        <v>1165766999.9999998</v>
       </c>
     </row>
     <row r="16" spans="1:32">
@@ -27051,7 +27051,7 @@
       </c>
       <c r="B21" s="36">
         <f>SUM(B15:AF15) / SUM($B$15:$AF$18)</f>
-        <v>0.64543423090865204</v>
+        <v>0.66481469544621774</v>
       </c>
     </row>
     <row r="22" spans="1:32">
@@ -27060,7 +27060,7 @@
       </c>
       <c r="B22" s="36">
         <f t="shared" ref="B22:B24" si="1">SUM(B16:AF16) / SUM($B$15:$AF$18)</f>
-        <v>0.12703753659699649</v>
+        <v>0.12009370081931435</v>
       </c>
     </row>
     <row r="23" spans="1:32">
@@ -27069,7 +27069,7 @@
       </c>
       <c r="B23" s="36">
         <f t="shared" si="1"/>
-        <v>0.18767644552984095</v>
+        <v>0.17741810416076614</v>
       </c>
     </row>
     <row r="24" spans="1:32">
@@ -27078,7 +27078,7 @@
       </c>
       <c r="B24" s="36">
         <f t="shared" si="1"/>
-        <v>3.9851786964509014E-2</v>
+        <v>3.7673499573699622E-2</v>
       </c>
     </row>
   </sheetData>

--- a/Sensitivity/Harmonization_SAF/Harmonization Sheets/Schmidt_Concawe_2024_Harmonization.xlsx
+++ b/Sensitivity/Harmonization_SAF/Harmonization Sheets/Schmidt_Concawe_2024_Harmonization.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="104" documentId="13_ncr:1_{409032AC-1BE5-8741-8011-1AD30BF05070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38530D46-E5A1-4666-9CB4-4BF82CAEBC5C}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs" sheetId="1" r:id="rId1"/>
@@ -1037,7 +1037,7 @@
         </row>
         <row r="34">
           <cell r="C34">
-            <v>523</v>
+            <v>497</v>
           </cell>
         </row>
       </sheetData>
@@ -1386,9 +1386,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:D33"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="24.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="C33" s="9">
         <f>[1]Inputs!$C$34</f>
-        <v>523</v>
+        <v>497</v>
       </c>
       <c r="D33" t="s">
         <v>29</v>
@@ -1798,16 +1798,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:T47"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.8984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.09765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.59765625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.8984375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
@@ -2537,11 +2537,11 @@
       </c>
       <c r="E14" s="32">
         <f>'MFSP CO2 Corrected'!B19</f>
-        <v>2.9084518536926556</v>
+        <v>2.8360093536926558</v>
       </c>
       <c r="F14" s="32">
         <f>'MFSP WACC Corrected'!B19</f>
-        <v>2.7128520104594722</v>
+        <v>2.6404095104594716</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="34" t="s">
@@ -2560,11 +2560,11 @@
       </c>
       <c r="L14" s="32">
         <f>'MFSP CO2 Corrected'!B42</f>
-        <v>2.9225495026684225</v>
+        <v>2.8501070026684241</v>
       </c>
       <c r="M14" s="32">
         <f>'MFSP WACC Corrected'!B42</f>
-        <v>2.7251695752088123</v>
+        <v>2.6527270752088126</v>
       </c>
       <c r="N14" s="5"/>
       <c r="O14" s="34" t="s">
@@ -2583,11 +2583,11 @@
       </c>
       <c r="S14" s="32">
         <f>'MFSP CO2 Corrected'!B65</f>
-        <v>2.9070388730814232</v>
+        <v>2.8345963730814239</v>
       </c>
       <c r="T14" s="16">
         <f>'MFSP WACC Corrected'!B65</f>
-        <v>2.7119102286140579</v>
+        <v>2.6394677286140569</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -2607,11 +2607,11 @@
       </c>
       <c r="E15" s="32">
         <f>E14/Inputs!$C$6</f>
-        <v>3.2316131707696174</v>
+        <v>3.1511215041029508</v>
       </c>
       <c r="F15" s="32">
         <f>F14/Inputs!$C$6</f>
-        <v>3.0142800116216355</v>
+        <v>2.9337883449549684</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="34" t="s">
@@ -2630,11 +2630,11 @@
       </c>
       <c r="L15" s="32">
         <f>L14/Inputs!$C$6</f>
-        <v>3.247277225187136</v>
+        <v>3.1667855585204712</v>
       </c>
       <c r="M15" s="32">
         <f>M14/Inputs!$C$6</f>
-        <v>3.0279661946764582</v>
+        <v>2.9474745280097916</v>
       </c>
       <c r="N15" s="5"/>
       <c r="O15" s="34" t="s">
@@ -2653,11 +2653,11 @@
       </c>
       <c r="S15" s="32">
         <f>S14/Inputs!$C$6</f>
-        <v>3.2300431923126922</v>
+        <v>3.1495515256460265</v>
       </c>
       <c r="T15" s="32">
         <f>T14/Inputs!$C$6</f>
-        <v>3.0132335873489531</v>
+        <v>2.9327419206822856</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -3017,11 +3017,11 @@
       </c>
       <c r="E21" s="33">
         <f>((E15-E16)/E20) * 10^6</f>
-        <v>533.23600180828578</v>
+        <v>505.21257178603594</v>
       </c>
       <c r="F21" s="33">
         <f>((F15-F16)/F20) * 10^6</f>
-        <v>457.5707704978235</v>
+        <v>429.54734047557349</v>
       </c>
       <c r="H21" s="22" t="s">
         <v>175</v>
@@ -3039,11 +3039,11 @@
       </c>
       <c r="L21" s="33">
         <f>((L15-L16)/L20) * 10^6</f>
-        <v>538.68949222552214</v>
+        <v>510.66606220327293</v>
       </c>
       <c r="M21" s="33">
         <f>((M15-M16)/M20) * 10^6</f>
-        <v>462.33565870291955</v>
+        <v>434.31222868066976</v>
       </c>
       <c r="O21" s="22" t="s">
         <v>175</v>
@@ -3061,11 +3061,11 @@
       </c>
       <c r="S21" s="33">
         <f>((S15-S16)/S20) * 10^6</f>
-        <v>532.68940880995365</v>
+        <v>504.66597878770415</v>
       </c>
       <c r="T21" s="33">
         <f>((T15-T16)/T20) * 10^6</f>
-        <v>457.20645455564602</v>
+        <v>429.18302453339584</v>
       </c>
     </row>
     <row r="23" spans="1:20">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="C33" s="9">
         <f>C32*Inputs!$C$33 * 10^-6</f>
-        <v>5.7907627174162202E-2</v>
+        <v>5.5028854121526985E-2</v>
       </c>
       <c r="H33" s="37" t="s">
         <v>183</v>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="J33" s="9">
         <f>J32*Inputs!$C$33 * 10^-6</f>
-        <v>6.5936120109336166E-2</v>
+        <v>6.2658225036979112E-2</v>
       </c>
       <c r="O33" s="37" t="s">
         <v>183</v>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="Q33" s="9">
         <f>Q32*Inputs!$C$33 * 10^-6</f>
-        <v>5.7879143587554881E-2</v>
+        <v>5.5001786544961337E-2</v>
       </c>
     </row>
     <row r="34" spans="1:17">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="C34" s="9">
         <f>F15+C33</f>
-        <v>3.0721876387957976</v>
+        <v>2.9888171990764953</v>
       </c>
       <c r="H34" s="37" t="s">
         <v>184</v>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="J34" s="9">
         <f>M15+J33</f>
-        <v>3.0939023147857942</v>
+        <v>3.0101327530467707</v>
       </c>
       <c r="O34" s="37" t="s">
         <v>184</v>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="Q34" s="9">
         <f>T15+Q33</f>
-        <v>3.0711127309365081</v>
+        <v>2.987743707227247</v>
       </c>
     </row>
     <row r="35" spans="1:17">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="C35" s="5">
         <f>(C34-C16) /C20 * 10^6</f>
-        <v>477.73149526688445</v>
+        <v>448.70581124081883</v>
       </c>
       <c r="H35" s="37" t="s">
         <v>185</v>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="J35" s="5">
         <f>(J34-J16) /J20 * 10^6</f>
-        <v>485.29152884876459</v>
+        <v>456.126889220794</v>
       </c>
       <c r="O35" s="37" t="s">
         <v>185</v>
@@ -3413,7 +3413,7 @@
       </c>
       <c r="Q35" s="5">
         <f>(Q34-Q16) /Q20 * 10^6</f>
-        <v>477.35726267334269</v>
+        <v>448.33207163568125</v>
       </c>
     </row>
     <row r="38" spans="1:17">
@@ -3554,13 +3554,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:F37"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="38.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.59765625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30.5" customWidth="1"/>
-    <col min="6" max="6" width="27.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="2" customFormat="1">
@@ -4124,12 +4124,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:AA44"/>
-  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="10.8984375" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="21" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.625" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.875" style="12" customWidth="1"/>
-    <col min="4" max="16384" width="10.875" style="12"/>
+    <col min="2" max="2" width="18.59765625" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.8984375" style="12" customWidth="1"/>
+    <col min="4" max="16384" width="10.8984375" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -5794,22 +5794,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:R58"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="29.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.8984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.875" customWidth="1"/>
+    <col min="4" max="4" width="9.8984375" customWidth="1"/>
     <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.8984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.09765625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.125" customWidth="1"/>
+    <col min="10" max="10" width="21.09765625" customWidth="1"/>
     <col min="11" max="11" width="10" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="29.875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="29.8984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.09765625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="8" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="25.375" customWidth="1"/>
+    <col min="16" max="16" width="25.3984375" customWidth="1"/>
     <col min="17" max="17" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7537,7 +7537,7 @@
       </c>
       <c r="B53" s="28">
         <f>(Inputs!$C$33*'Study Parameters'!$C$15 * 10^3) / 10^6</f>
-        <v>1165.7669999999998</v>
+        <v>1107.8129999999999</v>
       </c>
       <c r="C53" t="s">
         <v>97</v>
@@ -7547,7 +7547,7 @@
       </c>
       <c r="H53" s="28">
         <f>(Inputs!$C$33*'Study Parameters'!$C$15 * 10^3) / 10^6</f>
-        <v>1165.7669999999998</v>
+        <v>1107.8129999999999</v>
       </c>
       <c r="I53" t="s">
         <v>97</v>
@@ -7557,7 +7557,7 @@
       </c>
       <c r="N53" s="28">
         <f>(Inputs!$C$33*'Study Parameters'!$C$15 * 10^3) / 10^6</f>
-        <v>1165.7669999999998</v>
+        <v>1107.8129999999999</v>
       </c>
       <c r="O53" t="s">
         <v>97</v>
@@ -7569,7 +7569,7 @@
       </c>
       <c r="B54" s="29">
         <f>B52-B37+B53</f>
-        <v>1442.4152106372774</v>
+        <v>1384.4612106372774</v>
       </c>
       <c r="C54" s="8" t="s">
         <v>97</v>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="H54" s="29">
         <f>H52-H37+H53</f>
-        <v>1445.6452106372774</v>
+        <v>1387.6912106372774</v>
       </c>
       <c r="I54" s="8" t="s">
         <v>97</v>
@@ -7589,7 +7589,7 @@
       </c>
       <c r="N54" s="29">
         <f>N52-N37+N53</f>
-        <v>1443.4152106372774</v>
+        <v>1385.4612106372774</v>
       </c>
       <c r="O54" s="8" t="s">
         <v>97</v>
@@ -7688,11 +7688,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:AF65"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="26.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.8984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32">
@@ -12221,11 +12221,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:AF65"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="26.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.8984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32">
@@ -16756,11 +16756,11 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:AF65"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="26.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.8984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32">
@@ -17629,123 +17629,123 @@
       </c>
       <c r="C13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="D13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="E13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="F13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="G13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="H13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="I13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="J13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="K13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="L13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="M13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="N13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="O13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="P13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="Q13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="R13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="S13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="T13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="U13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="V13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="W13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="X13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="Y13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="Z13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="AA13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="AB13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="AC13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="AD13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="AE13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="AF13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
     </row>
     <row r="14" spans="1:32">
@@ -17885,123 +17885,123 @@
       </c>
       <c r="C15">
         <f>C13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!C12) +C14</f>
-        <v>1667428930.6138098</v>
+        <v>1613767819.5026987</v>
       </c>
       <c r="D15">
         <f>D13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!D12) +D14</f>
-        <v>1568497846.2079608</v>
+        <v>1518811632.2161913</v>
       </c>
       <c r="E15">
         <f>E13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!E12) +E14</f>
-        <v>1476894990.2766192</v>
+        <v>1430889236.5805364</v>
       </c>
       <c r="F15">
         <f>F13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!F12) +F14</f>
-        <v>1392077531.0809324</v>
+        <v>1349479610.9919667</v>
       </c>
       <c r="G15">
         <f>G13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!G12) +G14</f>
-        <v>1313542846.6404819</v>
+        <v>1274100328.0395877</v>
       </c>
       <c r="H15">
         <f>H13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!H12) +H14</f>
-        <v>1240825546.232657</v>
+        <v>1204304695.6762736</v>
       </c>
       <c r="I15">
         <f>I13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!I12) +I14</f>
-        <v>1173494712.5217085</v>
+        <v>1139679110.1546865</v>
       </c>
       <c r="J15">
         <f>J13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!J12) +J14</f>
-        <v>1111151347.9745336</v>
+        <v>1079840605.0421062</v>
       </c>
       <c r="K15">
         <f>K13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!K12) +K14</f>
-        <v>1053426010.4308532</v>
+        <v>1024434581.7897166</v>
       </c>
       <c r="L15">
         <f>L13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!L12) +L14</f>
-        <v>999976623.81633437</v>
+        <v>973132708.40787458</v>
       </c>
       <c r="M15">
         <f>M13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!M12) +M14</f>
-        <v>950486451.02511322</v>
+        <v>925630973.79505789</v>
       </c>
       <c r="N15">
         <f>N13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!N12) +N14</f>
-        <v>904662216.95916772</v>
+        <v>881647886.19059801</v>
       </c>
       <c r="O15">
         <f>O13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!O12) +O14</f>
-        <v>862232370.60181081</v>
+        <v>840922805.07535732</v>
       </c>
       <c r="P15">
         <f>P13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!P12) +P14</f>
-        <v>822945475.82648027</v>
+        <v>803214396.63531959</v>
       </c>
       <c r="Q15">
         <f>Q13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!Q12) +Q14</f>
-        <v>786568721.4048779</v>
+        <v>768299203.63528466</v>
       </c>
       <c r="R15">
         <f>R13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!R12) +R14</f>
-        <v>752886541.38487577</v>
+        <v>735970321.22784507</v>
       </c>
       <c r="S15">
         <f>S13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!S12) +S14</f>
-        <v>721699337.66265154</v>
+        <v>706036170.85058618</v>
       </c>
       <c r="T15">
         <f>T13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!T12) +T14</f>
-        <v>692822297.17911065</v>
+        <v>678319364.94571662</v>
       </c>
       <c r="U15">
         <f>U13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!U12) +U14</f>
-        <v>666084296.73138762</v>
+        <v>652655655.77454138</v>
       </c>
       <c r="V15">
         <f>V13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!V12) +V14</f>
-        <v>641326888.9094218</v>
+        <v>628892962.09752703</v>
       </c>
       <c r="W15">
         <f>W13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!W12) +W14</f>
-        <v>618403363.14834237</v>
+        <v>606890467.95214355</v>
       </c>
       <c r="X15">
         <f>X13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!X12) +X14</f>
-        <v>597177876.332528</v>
+        <v>586517788.18789947</v>
       </c>
       <c r="Y15">
         <f>Y13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!Y12) +Y14</f>
-        <v>577524647.79936659</v>
+        <v>567654195.81359947</v>
       </c>
       <c r="Z15">
         <f>Z13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!Z12) +Z14</f>
-        <v>559327213.97236538</v>
+        <v>550187906.57813644</v>
       </c>
       <c r="AA15">
         <f>AA13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AA12) +AA14</f>
-        <v>542477738.20662332</v>
+        <v>534015416.54530036</v>
       </c>
       <c r="AB15">
         <f>AB13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AB12) +AB14</f>
-        <v>526876371.75686234</v>
+        <v>519040888.73711884</v>
       </c>
       <c r="AC15">
         <f>AC13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AC12) +AC14</f>
-        <v>512430662.08115768</v>
+        <v>505175585.21102476</v>
       </c>
       <c r="AD15">
         <f>AD13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AD12) +AD14</f>
-        <v>499055004.9740237</v>
+        <v>492337341.20538217</v>
       </c>
       <c r="AE15">
         <f>AE13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AE12) +AE14</f>
-        <v>486670137.282233</v>
+        <v>480450078.23719454</v>
       </c>
       <c r="AF15">
         <f>AF13/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AF12) +AF14</f>
-        <v>475202667.1972416</v>
+        <v>469443353.26665044</v>
       </c>
     </row>
     <row r="16" spans="1:32">
@@ -18266,7 +18266,7 @@
       </c>
       <c r="B19">
         <f>SUM(B15:AF15) / SUM(B17:AF17)</f>
-        <v>2.9084518536926556</v>
+        <v>2.8360093536926558</v>
       </c>
     </row>
     <row r="21" spans="1:32" s="24" customFormat="1"/>
@@ -19136,123 +19136,123 @@
       </c>
       <c r="C36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="D36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="E36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="F36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="G36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="H36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="I36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="J36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="K36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="L36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="M36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="N36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="O36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="P36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="Q36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="R36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="S36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="T36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="U36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="V36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="W36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="X36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="Y36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="Z36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="AA36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="AB36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="AC36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="AD36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="AE36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="AF36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
     </row>
     <row r="37" spans="1:32">
@@ -19393,123 +19393,123 @@
       </c>
       <c r="C38">
         <f>C36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!C35) + C37</f>
-        <v>1673439804.0897179</v>
+        <v>1619778692.9786067</v>
       </c>
       <c r="D38">
         <f>D36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!D35) + D37</f>
-        <v>1574287183.3327029</v>
+        <v>1524600969.3409333</v>
       </c>
       <c r="E38">
         <f>E36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!E35) + E37</f>
-        <v>1482479201.1502817</v>
+        <v>1436473447.4541986</v>
       </c>
       <c r="F38">
         <f>F36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!F35) + F37</f>
-        <v>1397471810.2406321</v>
+        <v>1354873890.1516666</v>
       </c>
       <c r="G38">
         <f>G36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!G35) + G37</f>
-        <v>1318761263.1020679</v>
+        <v>1279318744.501174</v>
       </c>
       <c r="H38">
         <f>H36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!H35) + H37</f>
-        <v>1245881126.8626566</v>
+        <v>1209360276.3062735</v>
       </c>
       <c r="I38">
         <f>I36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!I35) + I37</f>
-        <v>1178399519.2335722</v>
+        <v>1144583916.8665504</v>
       </c>
       <c r="J38">
         <f>J36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!J35) + J37</f>
-        <v>1115916549.2066422</v>
+        <v>1084605806.2742147</v>
       </c>
       <c r="K38">
         <f>K36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!K35) + K37</f>
-        <v>1058061947.3298551</v>
+        <v>1029070518.6887186</v>
       </c>
       <c r="L38">
         <f>L36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!L35) + L37</f>
-        <v>1004492871.5180151</v>
+        <v>977648956.10955536</v>
       </c>
       <c r="M38">
         <f>M36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!M35) + M37</f>
-        <v>954891875.39594126</v>
+        <v>930036398.16588581</v>
       </c>
       <c r="N38">
         <f>N36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!N35) + N37</f>
-        <v>908965027.13476157</v>
+        <v>885950696.36619174</v>
       </c>
       <c r="O38">
         <f>O36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!O35) + O37</f>
-        <v>866440167.63366938</v>
+        <v>845130602.10721588</v>
       </c>
       <c r="P38">
         <f>P36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!P35) + P37</f>
-        <v>827065297.72525048</v>
+        <v>807334218.5340898</v>
       </c>
       <c r="Q38">
         <f>Q36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!Q35) + Q37</f>
-        <v>790607084.847085</v>
+        <v>772337567.07749176</v>
       </c>
       <c r="R38">
         <f>R36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!R35) + R37</f>
-        <v>756849480.33026516</v>
+        <v>739933260.17323446</v>
       </c>
       <c r="S38">
         <f>S36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!S35) + S37</f>
-        <v>725592439.11098742</v>
+        <v>709929272.29892194</v>
       </c>
       <c r="T38">
         <f>T36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!T35) + T37</f>
-        <v>696650734.27832294</v>
+        <v>682147802.04492903</v>
       </c>
       <c r="U38">
         <f>U36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!U35) + U37</f>
-        <v>669852859.43326306</v>
+        <v>656424218.47641683</v>
       </c>
       <c r="V38">
         <f>V36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!V35) + V37</f>
-        <v>645040012.35450411</v>
+        <v>632606085.54260945</v>
       </c>
       <c r="W38">
         <f>W36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!W35) + W37</f>
-        <v>622065153.94824576</v>
+        <v>610552258.75204706</v>
       </c>
       <c r="X38">
         <f>X36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!X35) + X37</f>
-        <v>600792136.90541399</v>
+        <v>590132048.76078546</v>
       </c>
       <c r="Y38">
         <f>Y36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!Y35) + Y37</f>
-        <v>581094898.90279198</v>
+        <v>571224446.91702485</v>
       </c>
       <c r="Z38">
         <f>Z36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!Z35) + Z37</f>
-        <v>562856715.56703079</v>
+        <v>553717408.17280197</v>
       </c>
       <c r="AA38">
         <f>AA36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AA35) + AA37</f>
-        <v>545969508.7746594</v>
+        <v>537507187.11333632</v>
       </c>
       <c r="AB38">
         <f>AB36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AB35) + AB37</f>
-        <v>530333206.18913031</v>
+        <v>522497723.16938674</v>
       </c>
       <c r="AC38">
         <f>AC36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AC35) + AC37</f>
-        <v>515855148.23956633</v>
+        <v>508600071.3694334</v>
       </c>
       <c r="AD38">
         <f>AD36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AD35) + AD37</f>
-        <v>502449539.02700704</v>
+        <v>495731875.25836551</v>
       </c>
       <c r="AE38">
         <f>AE36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AE35) + AE37</f>
-        <v>490036937.90426701</v>
+        <v>483816878.85922849</v>
       </c>
       <c r="AF38">
         <f>AF36/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AF35) + AF37</f>
-        <v>478543788.71654475</v>
+        <v>472784474.78595352</v>
       </c>
     </row>
     <row r="39" spans="1:32">
@@ -19775,7 +19775,7 @@
       </c>
       <c r="B42">
         <f>SUM(B38:AF38) / SUM(B40:AF40)</f>
-        <v>2.9225495026684225</v>
+        <v>2.8501070026684241</v>
       </c>
     </row>
     <row r="44" spans="1:32" s="24" customFormat="1"/>
@@ -20643,123 +20643,123 @@
       </c>
       <c r="C59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="D59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="E59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="F59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="G59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="H59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="I59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="J59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="K59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="L59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="M59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="N59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="O59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="P59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="Q59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="R59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="S59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="T59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="U59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="V59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="W59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="X59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="Y59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="Z59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="AA59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="AB59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="AC59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="AD59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="AE59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="AF59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
     </row>
     <row r="60" spans="1:32">
@@ -20899,123 +20899,123 @@
       </c>
       <c r="C61">
         <f>C59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!C58) + C60</f>
-        <v>1667555409.63925</v>
+        <v>1613894298.5281391</v>
       </c>
       <c r="D61">
         <f>D59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!D58) + D60</f>
-        <v>1568555738.1277771</v>
+        <v>1518869524.1360075</v>
       </c>
       <c r="E61">
         <f>E59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!E58) + E60</f>
-        <v>1476889375.6171539</v>
+        <v>1430883621.9210708</v>
       </c>
       <c r="F61">
         <f>F59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!F58) + F60</f>
-        <v>1392013114.0332434</v>
+        <v>1349415193.9442778</v>
       </c>
       <c r="G61">
         <f>G59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!G58) + G60</f>
-        <v>1313423982.9370301</v>
+        <v>1273981464.3361359</v>
       </c>
       <c r="H61">
         <f>H59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!H58) + H60</f>
-        <v>1240656268.9590547</v>
+        <v>1204135418.4026713</v>
       </c>
       <c r="I61">
         <f>I59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!I58) + I60</f>
-        <v>1173278756.016485</v>
+        <v>1139463153.6494632</v>
       </c>
       <c r="J61">
         <f>J59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!J58) + J60</f>
-        <v>1110892169.95855</v>
+        <v>1079581427.0261226</v>
       </c>
       <c r="K61">
         <f>K59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!K58) + K60</f>
-        <v>1053126812.4974992</v>
+        <v>1024135383.8563626</v>
       </c>
       <c r="L61">
         <f>L59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!L58) + L60</f>
-        <v>999640370.40393353</v>
+        <v>972796454.99547386</v>
       </c>
       <c r="M61">
         <f>M59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!M58) + M60</f>
-        <v>950115886.9839654</v>
+        <v>925260409.75391006</v>
       </c>
       <c r="N61">
         <f>N59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!N58) + N60</f>
-        <v>904259883.81732821</v>
+        <v>881245553.04875851</v>
       </c>
       <c r="O61">
         <f>O59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!O58) + O60</f>
-        <v>861800621.62599754</v>
+        <v>840491056.09954405</v>
       </c>
       <c r="P61">
         <f>P59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!P58) + P60</f>
-        <v>822486489.96735787</v>
+        <v>802755410.77619731</v>
       </c>
       <c r="Q61">
         <f>Q59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!Q58) + Q60</f>
-        <v>786084516.20935833</v>
+        <v>767814998.43976521</v>
       </c>
       <c r="R61">
         <f>R59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!R58) + R60</f>
-        <v>752378984.95195138</v>
+        <v>735462764.79492068</v>
       </c>
       <c r="S61">
         <f>S59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!S58) + S60</f>
-        <v>721170159.7136116</v>
+        <v>705506992.901546</v>
       </c>
       <c r="T61">
         <f>T59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!T58) + T60</f>
-        <v>692273099.30774128</v>
+        <v>677770167.07434726</v>
       </c>
       <c r="U61">
         <f>U59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!U58) + U60</f>
-        <v>665516561.89489841</v>
+        <v>652087920.93805218</v>
       </c>
       <c r="V61">
         <f>V59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!V58) + V60</f>
-        <v>640741990.21634042</v>
+        <v>628308063.40444565</v>
       </c>
       <c r="W61">
         <f>W59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!W58) + W60</f>
-        <v>617802571.99545324</v>
+        <v>606289676.79925442</v>
       </c>
       <c r="X61">
         <f>X59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!X58) + X60</f>
-        <v>596562369.93907619</v>
+        <v>585902281.79444766</v>
       </c>
       <c r="Y61">
         <f>Y59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!Y58) + Y60</f>
-        <v>576895516.18317151</v>
+        <v>567025064.19740438</v>
       </c>
       <c r="Z61">
         <f>Z59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!Z58) + Z60</f>
-        <v>558685466.40918589</v>
+        <v>549546159.01495695</v>
       </c>
       <c r="AA61">
         <f>AA59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AA58) + AA60</f>
-        <v>541824309.21105087</v>
+        <v>533361987.5497278</v>
       </c>
       <c r="AB61">
         <f>AB59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AB58) + AB60</f>
-        <v>526212126.62018514</v>
+        <v>518376643.60044163</v>
       </c>
       <c r="AC61">
         <f>AC59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AC58) + AC60</f>
-        <v>511756401.99901319</v>
+        <v>504501325.12888032</v>
       </c>
       <c r="AD61">
         <f>AD59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AD58) + AD60</f>
-        <v>498371471.79422438</v>
+        <v>491653808.02558279</v>
       </c>
       <c r="AE61">
         <f>AE59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AE58) + AE60</f>
-        <v>485978017.90090132</v>
+        <v>479757958.85586286</v>
       </c>
       <c r="AF61">
         <f>AF59/((1+'Study Parameters'!$C$4)^'MFSP Baseline'!AF58) + AF60</f>
-        <v>474502597.62930596</v>
+        <v>468743283.69871473</v>
       </c>
     </row>
     <row r="62" spans="1:32">
@@ -21280,7 +21280,7 @@
       </c>
       <c r="B65">
         <f>SUM(B61:AF61) / SUM(B63:AF63)</f>
-        <v>2.9070388730814232</v>
+        <v>2.8345963730814239</v>
       </c>
     </row>
   </sheetData>
@@ -21291,11 +21291,11 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:AF71"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="26.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.8984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32">
@@ -22164,123 +22164,123 @@
       </c>
       <c r="C13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="D13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="E13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="F13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="G13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="H13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="I13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="J13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="K13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="L13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="M13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="N13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="O13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="P13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="Q13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="R13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="S13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="T13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="U13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="V13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="W13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="X13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="Y13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="Z13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="AA13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="AB13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="AC13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="AD13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="AE13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
       <c r="AF13">
         <f>'Cost Components'!$B$54*10^6</f>
-        <v>1442415210.6372774</v>
+        <v>1384461210.6372774</v>
       </c>
     </row>
     <row r="14" spans="1:32">
@@ -22420,123 +22420,123 @@
       </c>
       <c r="C15">
         <f>C13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!C12) + C14</f>
-        <v>1649122402.2439387</v>
+        <v>1594959785.4215088</v>
       </c>
       <c r="D15">
         <f>D13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!D12) + D14</f>
-        <v>1560932110.7384715</v>
+        <v>1510312842.680126</v>
       </c>
       <c r="E15">
         <f>E13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!E12) + E14</f>
-        <v>1478511277.5557919</v>
+        <v>1431203550.3984594</v>
       </c>
       <c r="F15">
         <f>F13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!F12) + F14</f>
-        <v>1401482461.4972129</v>
+        <v>1357269632.3782105</v>
       </c>
       <c r="G15">
         <f>G13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!G12) + G14</f>
-        <v>1329492913.7789145</v>
+        <v>1288172512.7331181</v>
       </c>
       <c r="H15">
         <f>H13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!H12) + H14</f>
-        <v>1262212962.6403182</v>
+        <v>1223595765.4012561</v>
       </c>
       <c r="I15">
         <f>I13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!I12) + I14</f>
-        <v>1199334503.6322839</v>
+        <v>1163243665.0911045</v>
       </c>
       <c r="J15">
         <f>J13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!J12) + J14</f>
-        <v>1140569588.6715045</v>
+        <v>1106839833.0255423</v>
       </c>
       <c r="K15">
         <f>K13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!K12) + K14</f>
-        <v>1085649107.3997478</v>
+        <v>1054125971.2820261</v>
       </c>
       <c r="L15">
         <f>L13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!L12) + L14</f>
-        <v>1034321554.8093212</v>
+        <v>1004860679.9329457</v>
       </c>
       <c r="M15">
         <f>M13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!M12) + M14</f>
-        <v>986351879.4911654</v>
+        <v>958818351.56931925</v>
       </c>
       <c r="N15">
         <f>N13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!N12) + N14</f>
-        <v>941520407.23120689</v>
+        <v>915788138.14536929</v>
       </c>
       <c r="O15">
         <f>O13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!O12) + O14</f>
-        <v>899621835.02563787</v>
+        <v>875572985.41270566</v>
       </c>
       <c r="P15">
         <f>P13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!P12) + P14</f>
-        <v>860464290.90828395</v>
+        <v>837988730.52236581</v>
       </c>
       <c r="Q15">
         <f>Q13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!Q12) + Q14</f>
-        <v>823868455.28458834</v>
+        <v>802863258.66223502</v>
       </c>
       <c r="R15">
         <f>R13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!R12) + R14</f>
-        <v>789666739.74842453</v>
+        <v>770035714.8677206</v>
       </c>
       <c r="S15">
         <f>S13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!S12) + S14</f>
-        <v>757702519.62116861</v>
+        <v>739355767.3962115</v>
       </c>
       <c r="T15">
         <f>T13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!T12) + T14</f>
-        <v>727829416.69849944</v>
+        <v>710682919.29199743</v>
       </c>
       <c r="U15">
         <f>U13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!U12) + U14</f>
-        <v>699910628.92030382</v>
+        <v>683885864.98899364</v>
       </c>
       <c r="V15">
         <f>V13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!V12) + V14</f>
-        <v>673818303.89395308</v>
+        <v>658841889.00487804</v>
       </c>
       <c r="W15">
         <f>W13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!W12) + W14</f>
-        <v>649432953.40203619</v>
+        <v>635436303.97299433</v>
       </c>
       <c r="X15">
         <f>X13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!X12) + X14</f>
-        <v>626642906.21332908</v>
+        <v>613561925.43852341</v>
       </c>
       <c r="Y15">
         <f>Y13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!Y12) + Y14</f>
-        <v>605343796.69117272</v>
+        <v>593118581.01378429</v>
       </c>
       <c r="Z15">
         <f>Z13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!Z12) + Z14</f>
-        <v>585438086.85738182</v>
+        <v>574012651.64486933</v>
       </c>
       <c r="AA15">
         <f>AA13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!AA12) + AA14</f>
-        <v>566834619.72299767</v>
+        <v>556156642.88887382</v>
       </c>
       <c r="AB15">
         <f>AB13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!AB12) + AB14</f>
-        <v>549448201.84039581</v>
+        <v>539468784.23841095</v>
       </c>
       <c r="AC15">
         <f>AC13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!AC12) + AC14</f>
-        <v>533199213.16506696</v>
+        <v>523872654.65853894</v>
       </c>
       <c r="AD15">
         <f>AD13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!AD12) + AD14</f>
-        <v>518013242.44046056</v>
+        <v>509296832.62127554</v>
       </c>
       <c r="AE15">
         <f>AE13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!AE12) + AE14</f>
-        <v>503820746.43615544</v>
+        <v>495674569.03504795</v>
       </c>
       <c r="AF15">
         <f>AF13/((1+'Cost Components'!$B$55)^'MFSP Baseline'!AF12) + AF14</f>
-        <v>490556731.47886097</v>
+        <v>482943481.57128388</v>
       </c>
     </row>
     <row r="16" spans="1:32">
@@ -22801,7 +22801,7 @@
       </c>
       <c r="B19">
         <f>SUM(B15:AF15) / SUM(B17:AF17)</f>
-        <v>2.7128520104594722</v>
+        <v>2.6404095104594716</v>
       </c>
     </row>
     <row r="21" spans="1:32" s="24" customFormat="1"/>
@@ -23671,123 +23671,123 @@
       </c>
       <c r="C36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="D36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="E36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="F36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="G36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="H36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="I36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="J36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="K36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="L36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="M36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="N36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="O36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="P36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="Q36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="R36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="S36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="T36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="U36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="V36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="W36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="X36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="Y36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="Z36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="AA36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="AB36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="AC36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="AD36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="AE36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
       <c r="AF36">
         <f>'Cost Components'!$H$54*10^6</f>
-        <v>1445645210.6372774</v>
+        <v>1387691210.6372774</v>
       </c>
     </row>
     <row r="37" spans="1:32">
@@ -23928,123 +23928,123 @@
       </c>
       <c r="C38">
         <f>C36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!C35) + C37</f>
-        <v>1654881031.5521016</v>
+        <v>1600718414.7296717</v>
       </c>
       <c r="D38">
         <f>D36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!D35) + D37</f>
-        <v>1566493255.5501719</v>
+        <v>1515873987.4918261</v>
       </c>
       <c r="E38">
         <f>E36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!E35) + E37</f>
-        <v>1483887857.417527</v>
+        <v>1436580130.2601945</v>
       </c>
       <c r="F38">
         <f>F36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!F35) + F37</f>
-        <v>1406686550.7515042</v>
+        <v>1362473721.6325018</v>
       </c>
       <c r="G38">
         <f>G36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!G35) + G37</f>
-        <v>1334535796.8580246</v>
+        <v>1293215395.812228</v>
       </c>
       <c r="H38">
         <f>H36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!H35) + H37</f>
-        <v>1267105185.7426233</v>
+        <v>1228487988.503561</v>
       </c>
       <c r="I38">
         <f>I36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!I35) + I37</f>
-        <v>1204085923.0179491</v>
+        <v>1167995084.4767694</v>
       </c>
       <c r="J38">
         <f>J36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!J35) + J37</f>
-        <v>1145189415.7986274</v>
+        <v>1111459660.1526651</v>
       </c>
       <c r="K38">
         <f>K36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!K35) + K37</f>
-        <v>1090145951.1076725</v>
+        <v>1058622814.9899507</v>
       </c>
       <c r="L38">
         <f>L36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!L35) + L37</f>
-        <v>1038703460.7422941</v>
+        <v>1009242585.8659186</v>
       </c>
       <c r="M38">
         <f>M36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!M35) + M37</f>
-        <v>990626366.94287515</v>
+        <v>963092839.02102876</v>
       </c>
       <c r="N38">
         <f>N36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!N35) + N37</f>
-        <v>945694503.57893205</v>
+        <v>919962234.49309468</v>
       </c>
       <c r="O38">
         <f>O36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!O35) + O37</f>
-        <v>903702107.91169572</v>
+        <v>879653258.29876328</v>
       </c>
       <c r="P38">
         <f>P36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!P35) + P37</f>
-        <v>864456878.31614757</v>
+        <v>841981317.93022966</v>
       </c>
       <c r="Q38">
         <f>Q36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!Q35) + Q37</f>
-        <v>827779093.64741099</v>
+        <v>806773897.02505767</v>
       </c>
       <c r="R38">
         <f>R36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!R35) + R37</f>
-        <v>793500790.21868539</v>
+        <v>773869765.33798122</v>
       </c>
       <c r="S38">
         <f>S36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!S35) + S37</f>
-        <v>761464992.62174535</v>
+        <v>743118240.39678836</v>
       </c>
       <c r="T38">
         <f>T36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!T35) + T37</f>
-        <v>731524994.86759591</v>
+        <v>714378497.46109402</v>
       </c>
       <c r="U38">
         <f>U36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!U35) + U37</f>
-        <v>703543688.55530667</v>
+        <v>687518924.6239965</v>
       </c>
       <c r="V38">
         <f>V36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!V35) + V37</f>
-        <v>677392934.9924196</v>
+        <v>662416520.10334468</v>
       </c>
       <c r="W38">
         <f>W36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!W35) + W37</f>
-        <v>652952978.39159048</v>
+        <v>638956328.96254849</v>
       </c>
       <c r="X38">
         <f>X36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!X35) + X37</f>
-        <v>630111897.45623612</v>
+        <v>617030916.68143058</v>
       </c>
       <c r="Y38">
         <f>Y36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!Y35) + Y37</f>
-        <v>608765092.84375548</v>
+        <v>596539877.16636705</v>
       </c>
       <c r="Z38">
         <f>Z36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!Z35) + Z37</f>
-        <v>588814808.15919423</v>
+        <v>577389372.94668162</v>
       </c>
       <c r="AA38">
         <f>AA36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!AA35) + AA37</f>
-        <v>570169682.28577232</v>
+        <v>559491705.45164847</v>
       </c>
       <c r="AB38">
         <f>AB36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!AB35) + AB37</f>
-        <v>552744331.0022006</v>
+        <v>542764913.40021563</v>
       </c>
       <c r="AC38">
         <f>AC36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!AC35) + AC37</f>
-        <v>536458955.97082496</v>
+        <v>527132397.46429706</v>
       </c>
       <c r="AD38">
         <f>AD36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!AD35) + AD37</f>
-        <v>521238979.30598807</v>
+        <v>512522569.48680305</v>
       </c>
       <c r="AE38">
         <f>AE36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!AE35) + AE37</f>
-        <v>507014702.04913116</v>
+        <v>498868524.64802366</v>
       </c>
       <c r="AF38">
         <f>AF36/((1+'Cost Components'!$H$55)^'MFSP Baseline'!AF35) + AF37</f>
-        <v>493720984.98664808</v>
+        <v>486107735.07907093</v>
       </c>
     </row>
     <row r="39" spans="1:32">
@@ -24310,7 +24310,7 @@
       </c>
       <c r="B42">
         <f>SUM(B38:AF38) / SUM(B40:AF40)</f>
-        <v>2.7251695752088123</v>
+        <v>2.6527270752088126</v>
       </c>
     </row>
     <row r="44" spans="1:32" s="24" customFormat="1"/>
@@ -25178,123 +25178,123 @@
       </c>
       <c r="C59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="D59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="E59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="F59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="G59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="H59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="I59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="J59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="K59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="L59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="M59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="N59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="O59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="P59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="Q59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="R59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="S59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="T59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="U59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="V59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="W59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="X59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="Y59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="Z59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="AA59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="AB59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="AC59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="AD59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="AE59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
       <c r="AF59">
         <f>'Cost Components'!$N$54*10^6</f>
-        <v>1443415210.6372774</v>
+        <v>1385461210.6372774</v>
       </c>
     </row>
     <row r="60" spans="1:32">
@@ -25434,123 +25434,123 @@
       </c>
       <c r="C61">
         <f>C59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!C58) + C60</f>
-        <v>1649331704.0515912</v>
+        <v>1595169087.2291613</v>
       </c>
       <c r="D61">
         <f>D59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!D58) + D60</f>
-        <v>1561080271.8351448</v>
+        <v>1510461003.7767992</v>
       </c>
       <c r="E61">
         <f>E59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!E58) + E60</f>
-        <v>1478602297.8010828</v>
+        <v>1431294570.6437504</v>
       </c>
       <c r="F61">
         <f>F59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!F58) + F60</f>
-        <v>1401520079.0776606</v>
+        <v>1357307249.9586582</v>
       </c>
       <c r="G61">
         <f>G59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!G58) + G60</f>
-        <v>1329480622.3267984</v>
+        <v>1288160221.2810018</v>
       </c>
       <c r="H61">
         <f>H59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!H58) + H60</f>
-        <v>1262154027.2325349</v>
+        <v>1223536829.9934726</v>
       </c>
       <c r="I61">
         <f>I59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!I58) + I60</f>
-        <v>1199231975.7425685</v>
+        <v>1163141137.2013891</v>
       </c>
       <c r="J61">
         <f>J59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!J58) + J60</f>
-        <v>1140426320.1444697</v>
+        <v>1106696564.4985075</v>
       </c>
       <c r="K61">
         <f>K59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!K58) + K60</f>
-        <v>1085467763.5107322</v>
+        <v>1053944627.3930104</v>
       </c>
       <c r="L61">
         <f>L59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!L58) + L60</f>
-        <v>1034104626.469856</v>
+        <v>1004643751.5934806</v>
       </c>
       <c r="M61">
         <f>M59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!M58) + M60</f>
-        <v>986101694.65595305</v>
+        <v>958568166.73410678</v>
       </c>
       <c r="N61">
         <f>N59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!N58) + N60</f>
-        <v>941239141.55884755</v>
+        <v>915506872.47301006</v>
       </c>
       <c r="O61">
         <f>O59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!O58) + O60</f>
-        <v>899311521.84192646</v>
+        <v>875262672.22899413</v>
       </c>
       <c r="P61">
         <f>P59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!P58) + P60</f>
-        <v>860126830.51770127</v>
+        <v>837651270.13178325</v>
       </c>
       <c r="Q61">
         <f>Q59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!Q58) + Q60</f>
-        <v>823505623.67263079</v>
+        <v>802500427.05027747</v>
       </c>
       <c r="R61">
         <f>R59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!R58) + R60</f>
-        <v>789280196.71462119</v>
+        <v>769649171.83391714</v>
       </c>
       <c r="S61">
         <f>S59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!S58) + S60</f>
-        <v>757293816.38003278</v>
+        <v>738947064.15507567</v>
       </c>
       <c r="T61">
         <f>T59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!T58) + T60</f>
-        <v>727400002.98322105</v>
+        <v>710253505.57671905</v>
       </c>
       <c r="U61">
         <f>U59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!U58) + U60</f>
-        <v>699461859.62171483</v>
+        <v>683437095.69040465</v>
       </c>
       <c r="V61">
         <f>V59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!V58) + V60</f>
-        <v>673351445.265167</v>
+        <v>658375030.37609196</v>
       </c>
       <c r="W61">
         <f>W59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!W58) + W60</f>
-        <v>648949188.85717821</v>
+        <v>634952539.42813623</v>
       </c>
       <c r="X61">
         <f>X59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!X58) + X60</f>
-        <v>626143341.74690843</v>
+        <v>613062360.97210288</v>
       </c>
       <c r="Y61">
         <f>Y59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!Y58) + Y60</f>
-        <v>604829465.94291806</v>
+        <v>592604250.26552963</v>
       </c>
       <c r="Z61">
         <f>Z59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!Z58) + Z60</f>
-        <v>584909955.84573054</v>
+        <v>573484520.63321805</v>
       </c>
       <c r="AA61">
         <f>AA59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!AA58) + AA60</f>
-        <v>566293591.26891994</v>
+        <v>555615614.43479609</v>
       </c>
       <c r="AB61">
         <f>AB59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!AB58) + AB60</f>
-        <v>548895119.70180726</v>
+        <v>538915702.0998224</v>
       </c>
       <c r="AC61">
         <f>AC59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!AC58) + AC60</f>
-        <v>532634865.90076733</v>
+        <v>523308307.39423943</v>
       </c>
       <c r="AD61">
         <f>AD59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!AD58) + AD60</f>
-        <v>517438367.02129084</v>
+        <v>508721957.20210582</v>
       </c>
       <c r="AE61">
         <f>AE59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!AE58) + AE60</f>
-        <v>503236031.6199109</v>
+        <v>495089854.21880341</v>
       </c>
       <c r="AF61">
         <f>AF59/((1+'Cost Components'!$N$55)^'MFSP Baseline'!AF58) + AF60</f>
-        <v>489962820.96441561</v>
+        <v>482349571.05683851</v>
       </c>
     </row>
     <row r="62" spans="1:32">
@@ -25815,7 +25815,7 @@
       </c>
       <c r="B65">
         <f>SUM(B61:AF61) / SUM(B63:AF63)</f>
-        <v>2.7119102286140579</v>
+        <v>2.6394677286140569</v>
       </c>
     </row>
     <row r="71" spans="1:32">
@@ -25858,11 +25858,11 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B055BC8F-95DE-8D40-846F-5575FFAD0FB7}">
   <dimension ref="A1:AF24"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.09765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32">
@@ -26536,123 +26536,123 @@
       </c>
       <c r="C15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!C13</f>
-        <v>1165766999.9999998</v>
+        <v>1107812999.9999998</v>
       </c>
       <c r="D15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!D13</f>
-        <v>1165766999.9999998</v>
+        <v>1107812999.9999998</v>
       </c>
       <c r="E15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!E13</f>
-        <v>1165766999.9999998</v>
+        <v>1107812999.9999998</v>
       </c>
       <c r="F15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!F13</f>
-        <v>1165766999.9999998</v>
+        <v>1107812999.9999998</v>
       </c>
       <c r="G15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!G13</f>
-        <v>1165766999.9999998</v>
+        <v>1107812999.9999998</v>
       </c>
       <c r="H15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!H13</f>
-        <v>1165766999.9999998</v>
+        <v>1107812999.9999998</v>
       </c>
       <c r="I15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!I13</f>
-        <v>1165766999.9999998</v>
+        <v>1107812999.9999998</v>
       </c>
       <c r="J15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!J13</f>
-        <v>1165766999.9999998</v>
+        <v>1107812999.9999998</v>
       </c>
       <c r="K15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!K13</f>
-        <v>1165766999.9999998</v>
+        <v>1107812999.9999998</v>
       </c>
       <c r="L15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!L13</f>
-        <v>1165766999.9999998</v>
+        <v>1107812999.9999998</v>
       </c>
       <c r="M15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!M13</f>
-        <v>1165766999.9999998</v>
+        <v>1107812999.9999998</v>
       </c>
       <c r="N15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!N13</f>
-        <v>1165766999.9999998</v>
+        <v>1107812999.9999998</v>
       </c>
       <c r="O15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!O13</f>
-        <v>1165766999.9999998</v>
+        <v>1107812999.9999998</v>
       </c>
       <c r="P15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!P13</f>
-        <v>1165766999.9999998</v>
+        <v>1107812999.9999998</v>
       </c>
       <c r="Q15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!Q13</f>
-        <v>1165766999.9999998</v>
+        <v>1107812999.9999998</v>
       </c>
       <c r="R15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!R13</f>
-        <v>1165766999.9999998</v>
+        <v>1107812999.9999998</v>
       </c>
       <c r="S15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!S13</f>
-        <v>1165766999.9999998</v>
+        <v>1107812999.9999998</v>
       </c>
       <c r="T15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!T13</f>
-        <v>1165766999.9999998</v>
+        <v>1107812999.9999998</v>
       </c>
       <c r="U15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!U13</f>
-        <v>1165766999.9999998</v>
+        <v>1107812999.9999998</v>
       </c>
       <c r="V15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!V13</f>
-        <v>1165766999.9999998</v>
+        <v>1107812999.9999998</v>
       </c>
       <c r="W15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!W13</f>
-        <v>1165766999.9999998</v>
+        <v>1107812999.9999998</v>
       </c>
       <c r="X15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!X13</f>
-        <v>1165766999.9999998</v>
+        <v>1107812999.9999998</v>
       </c>
       <c r="Y15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!Y13</f>
-        <v>1165766999.9999998</v>
+        <v>1107812999.9999998</v>
       </c>
       <c r="Z15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!Z13</f>
-        <v>1165766999.9999998</v>
+        <v>1107812999.9999998</v>
       </c>
       <c r="AA15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!AA13</f>
-        <v>1165766999.9999998</v>
+        <v>1107812999.9999998</v>
       </c>
       <c r="AB15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!AB13</f>
-        <v>1165766999.9999998</v>
+        <v>1107812999.9999998</v>
       </c>
       <c r="AC15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!AC13</f>
-        <v>1165766999.9999998</v>
+        <v>1107812999.9999998</v>
       </c>
       <c r="AD15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!AD13</f>
-        <v>1165766999.9999998</v>
+        <v>1107812999.9999998</v>
       </c>
       <c r="AE15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!AE13</f>
-        <v>1165766999.9999998</v>
+        <v>1107812999.9999998</v>
       </c>
       <c r="AF15">
         <f>('Cost Components'!$B$53 * 10^6) / (1+'Cost Components'!$B$55) ^'Cost Breakdown'!AF13</f>
-        <v>1165766999.9999998</v>
+        <v>1107812999.9999998</v>
       </c>
     </row>
     <row r="16" spans="1:32">
@@ -27051,7 +27051,7 @@
       </c>
       <c r="B21" s="36">
         <f>SUM(B15:AF15) / SUM($B$15:$AF$18)</f>
-        <v>0.66481469544621774</v>
+        <v>0.65335816141753911</v>
       </c>
     </row>
     <row r="22" spans="1:32">
@@ -27060,7 +27060,7 @@
       </c>
       <c r="B22" s="36">
         <f t="shared" ref="B22:B24" si="1">SUM(B16:AF16) / SUM($B$15:$AF$18)</f>
-        <v>0.12009370081931435</v>
+        <v>0.124198467798577</v>
       </c>
     </row>
     <row r="23" spans="1:32">
@@ -27069,7 +27069,7 @@
       </c>
       <c r="B23" s="36">
         <f t="shared" si="1"/>
-        <v>0.17741810416076614</v>
+        <v>0.18348220219849909</v>
       </c>
     </row>
     <row r="24" spans="1:32">
@@ -27078,7 +27078,7 @@
       </c>
       <c r="B24" s="36">
         <f t="shared" si="1"/>
-        <v>3.7673499573699622E-2</v>
+        <v>3.8961168585382851E-2</v>
       </c>
     </row>
   </sheetData>
